--- a/Grids Germany/No leap years/Saxony insights/[Saxony][Manhattan][Raw]Yearly_U_test.xlsx
+++ b/Grids Germany/No leap years/Saxony insights/[Saxony][Manhattan][Raw]Yearly_U_test.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,62 +429,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>YEAR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>mean_P1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>sd_P1</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>n_P1</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>mean_P2</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>sd_P2</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>n_P2</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>U_statistic</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>p_Bonferroni</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Significant</t>
         </is>
@@ -488,28 +500,28 @@
         <v>1996</v>
       </c>
       <c r="C2" t="n">
-        <v>8.469754084135847</v>
+        <v>8.386545055238027</v>
       </c>
       <c r="D2" t="n">
-        <v>5.096979905634888</v>
+        <v>5.16710253746185</v>
       </c>
       <c r="E2" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F2" t="n">
-        <v>9.891788624229887</v>
+        <v>9.877147909777646</v>
       </c>
       <c r="G2" t="n">
-        <v>2.428613219803454</v>
+        <v>2.436477277645661</v>
       </c>
       <c r="H2" t="n">
         <v>15</v>
       </c>
       <c r="I2" t="n">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4048481863452824</v>
+        <v>0.3663301448509562</v>
       </c>
       <c r="K2" t="n">
         <v>1</v>
@@ -528,28 +540,28 @@
         <v>1997</v>
       </c>
       <c r="C3" t="n">
-        <v>8.782970744626169</v>
+        <v>8.665265753915032</v>
       </c>
       <c r="D3" t="n">
-        <v>5.880281723210724</v>
+        <v>5.712142009622185</v>
       </c>
       <c r="E3" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F3" t="n">
-        <v>10.83068367183578</v>
+        <v>10.39838517627381</v>
       </c>
       <c r="G3" t="n">
-        <v>2.063560056379712</v>
+        <v>1.82792849291061</v>
       </c>
       <c r="H3" t="n">
         <v>15</v>
       </c>
       <c r="I3" t="n">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="J3" t="n">
-        <v>0.08255452636650192</v>
+        <v>0.09296720669982936</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
@@ -568,28 +580,28 @@
         <v>1998</v>
       </c>
       <c r="C4" t="n">
-        <v>11.22860892897619</v>
+        <v>11.25399837075242</v>
       </c>
       <c r="D4" t="n">
-        <v>4.079206131121895</v>
+        <v>4.136477100617287</v>
       </c>
       <c r="E4" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F4" t="n">
-        <v>11.05853012936236</v>
+        <v>10.59778191169642</v>
       </c>
       <c r="G4" t="n">
-        <v>2.475026570958029</v>
+        <v>2.994482036297156</v>
       </c>
       <c r="H4" t="n">
         <v>15</v>
       </c>
       <c r="I4" t="n">
-        <v>366</v>
+        <v>384</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8947115574974374</v>
+        <v>0.7998221876154478</v>
       </c>
       <c r="K4" t="n">
         <v>1</v>
@@ -608,31 +620,31 @@
         <v>1999</v>
       </c>
       <c r="C5" t="n">
-        <v>9.837587112542424</v>
+        <v>9.789345610798961</v>
       </c>
       <c r="D5" t="n">
-        <v>3.03166787702692</v>
+        <v>2.946045476663019</v>
       </c>
       <c r="E5" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F5" t="n">
-        <v>15.94521747175242</v>
+        <v>15.54429684118486</v>
       </c>
       <c r="G5" t="n">
-        <v>1.797743514829136</v>
+        <v>2.246814050432507</v>
       </c>
       <c r="H5" t="n">
         <v>15</v>
       </c>
       <c r="I5" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="J5" t="n">
-        <v>5.277223998338812e-08</v>
+        <v>3.338839399886424e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.583167199501643e-06</v>
+        <v>1.001651819965927e-05</v>
       </c>
       <c r="L5" t="b">
         <v>1</v>
@@ -648,28 +660,28 @@
         <v>2000</v>
       </c>
       <c r="C6" t="n">
-        <v>12.62638004067425</v>
+        <v>12.69629443232591</v>
       </c>
       <c r="D6" t="n">
-        <v>5.299624400133959</v>
+        <v>5.278428886529648</v>
       </c>
       <c r="E6" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F6" t="n">
-        <v>12.50144636571204</v>
+        <v>12.64986717324429</v>
       </c>
       <c r="G6" t="n">
-        <v>2.83519294442837</v>
+        <v>2.796309474172748</v>
       </c>
       <c r="H6" t="n">
         <v>15</v>
       </c>
       <c r="I6" t="n">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6348694025571869</v>
+        <v>0.6120464418511691</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
@@ -688,31 +700,31 @@
         <v>2001</v>
       </c>
       <c r="C7" t="n">
-        <v>9.54109719270474</v>
+        <v>9.560642838059483</v>
       </c>
       <c r="D7" t="n">
-        <v>4.987576996396085</v>
+        <v>4.980240718823767</v>
       </c>
       <c r="E7" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F7" t="n">
-        <v>12.09507536276513</v>
+        <v>12.63651251389686</v>
       </c>
       <c r="G7" t="n">
-        <v>2.347371020557338</v>
+        <v>2.54744952742508</v>
       </c>
       <c r="H7" t="n">
         <v>15</v>
       </c>
       <c r="I7" t="n">
-        <v>257</v>
+        <v>222</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0673288525154592</v>
+        <v>0.02155930376220828</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0.6467791128662485</v>
       </c>
       <c r="L7" t="b">
         <v>0</v>
@@ -728,28 +740,28 @@
         <v>2002</v>
       </c>
       <c r="C8" t="n">
-        <v>10.21939399309625</v>
+        <v>10.05977933809033</v>
       </c>
       <c r="D8" t="n">
-        <v>4.442241263819827</v>
+        <v>4.378786986429251</v>
       </c>
       <c r="E8" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F8" t="n">
-        <v>9.837771418191085</v>
+        <v>9.863568425732293</v>
       </c>
       <c r="G8" t="n">
-        <v>1.866898035679396</v>
+        <v>1.905825229240338</v>
       </c>
       <c r="H8" t="n">
         <v>15</v>
       </c>
       <c r="I8" t="n">
-        <v>393</v>
+        <v>375</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7852570955409328</v>
+        <v>0.9116638948284465</v>
       </c>
       <c r="K8" t="n">
         <v>1</v>
@@ -768,28 +780,28 @@
         <v>2003</v>
       </c>
       <c r="C9" t="n">
-        <v>10.04426018003328</v>
+        <v>9.986124943550308</v>
       </c>
       <c r="D9" t="n">
-        <v>5.569542024009166</v>
+        <v>5.639458902099336</v>
       </c>
       <c r="E9" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F9" t="n">
-        <v>14.0335099322414</v>
+        <v>13.65683458505401</v>
       </c>
       <c r="G9" t="n">
-        <v>3.891317425486011</v>
+        <v>3.783649029013247</v>
       </c>
       <c r="H9" t="n">
         <v>15</v>
       </c>
       <c r="I9" t="n">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0391105188183906</v>
+        <v>0.0683660631919407</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
@@ -808,19 +820,19 @@
         <v>2004</v>
       </c>
       <c r="C10" t="n">
-        <v>10.05770151616938</v>
+        <v>10.0408818699081</v>
       </c>
       <c r="D10" t="n">
-        <v>3.154678224265318</v>
+        <v>3.146506498539564</v>
       </c>
       <c r="E10" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F10" t="n">
-        <v>11.39863098023377</v>
+        <v>11.25831072946215</v>
       </c>
       <c r="G10" t="n">
-        <v>2.02963258462574</v>
+        <v>1.956314408835219</v>
       </c>
       <c r="H10" t="n">
         <v>15</v>
@@ -829,7 +841,7 @@
         <v>280</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1411929728237963</v>
+        <v>0.1679483459853076</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
@@ -848,31 +860,31 @@
         <v>2005</v>
       </c>
       <c r="C11" t="n">
-        <v>9.521804739587068</v>
+        <v>9.44733116817738</v>
       </c>
       <c r="D11" t="n">
-        <v>3.625307892912963</v>
+        <v>3.659732896819404</v>
       </c>
       <c r="E11" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F11" t="n">
-        <v>11.44217359636731</v>
+        <v>11.61778301125909</v>
       </c>
       <c r="G11" t="n">
-        <v>2.257197703738032</v>
+        <v>2.112217517329908</v>
       </c>
       <c r="H11" t="n">
         <v>15</v>
       </c>
       <c r="I11" t="n">
-        <v>236</v>
+        <v>212</v>
       </c>
       <c r="J11" t="n">
-        <v>0.03104916222100544</v>
+        <v>0.01402863069426756</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9314748666301631</v>
+        <v>0.4208589208280267</v>
       </c>
       <c r="L11" t="b">
         <v>0</v>
@@ -888,31 +900,31 @@
         <v>2006</v>
       </c>
       <c r="C12" t="n">
-        <v>10.22970542244096</v>
+        <v>10.23093914483574</v>
       </c>
       <c r="D12" t="n">
-        <v>3.899402739006975</v>
+        <v>3.918420487496435</v>
       </c>
       <c r="E12" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F12" t="n">
-        <v>15.91275379744522</v>
+        <v>15.54190075931588</v>
       </c>
       <c r="G12" t="n">
-        <v>1.319845984543472</v>
+        <v>1.403078038894047</v>
       </c>
       <c r="H12" t="n">
         <v>15</v>
       </c>
       <c r="I12" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="J12" t="n">
-        <v>1.61188665175849e-07</v>
+        <v>8.269072865267855e-07</v>
       </c>
       <c r="K12" t="n">
-        <v>4.83565995527547e-06</v>
+        <v>2.480721859580357e-05</v>
       </c>
       <c r="L12" t="b">
         <v>1</v>
@@ -928,28 +940,28 @@
         <v>2007</v>
       </c>
       <c r="C13" t="n">
-        <v>11.34770468004601</v>
+        <v>11.32896163629039</v>
       </c>
       <c r="D13" t="n">
-        <v>3.653110102741485</v>
+        <v>3.554105528807592</v>
       </c>
       <c r="E13" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F13" t="n">
-        <v>11.99386195852435</v>
+        <v>12.04630177713269</v>
       </c>
       <c r="G13" t="n">
-        <v>1.917048639008921</v>
+        <v>1.912735524746714</v>
       </c>
       <c r="H13" t="n">
         <v>15</v>
       </c>
       <c r="I13" t="n">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4982193853452911</v>
+        <v>0.5261179686617201</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
@@ -968,28 +980,28 @@
         <v>2008</v>
       </c>
       <c r="C14" t="n">
-        <v>9.633325561027648</v>
+        <v>9.612062801736041</v>
       </c>
       <c r="D14" t="n">
-        <v>3.80268375855831</v>
+        <v>3.834962581283978</v>
       </c>
       <c r="E14" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F14" t="n">
-        <v>9.48402855164616</v>
+        <v>9.476845366402133</v>
       </c>
       <c r="G14" t="n">
-        <v>1.0285039597875</v>
+        <v>1.044354034489132</v>
       </c>
       <c r="H14" t="n">
         <v>15</v>
       </c>
       <c r="I14" t="n">
-        <v>410</v>
+        <v>399</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5911541483740381</v>
+        <v>0.6232101159683183</v>
       </c>
       <c r="K14" t="n">
         <v>1</v>
@@ -1008,28 +1020,28 @@
         <v>2009</v>
       </c>
       <c r="C15" t="n">
-        <v>12.11521900508077</v>
+        <v>12.05885002411786</v>
       </c>
       <c r="D15" t="n">
-        <v>2.774077727273563</v>
+        <v>2.56039012941634</v>
       </c>
       <c r="E15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F15" t="n">
-        <v>13.3881029248651</v>
+        <v>13.17486898833987</v>
       </c>
       <c r="G15" t="n">
-        <v>2.333410772762962</v>
+        <v>2.40135116430949</v>
       </c>
       <c r="H15" t="n">
         <v>15</v>
       </c>
       <c r="I15" t="n">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1454498443614571</v>
+        <v>0.2163883153007072</v>
       </c>
       <c r="K15" t="n">
         <v>1</v>
@@ -1048,31 +1060,31 @@
         <v>2010</v>
       </c>
       <c r="C16" t="n">
-        <v>8.799185340400209</v>
+        <v>8.614422826526779</v>
       </c>
       <c r="D16" t="n">
-        <v>2.941360767103613</v>
+        <v>2.950896487428647</v>
       </c>
       <c r="E16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F16" t="n">
-        <v>10.74148826820781</v>
+        <v>10.87969762470956</v>
       </c>
       <c r="G16" t="n">
-        <v>2.715180749464023</v>
+        <v>2.690872926781228</v>
       </c>
       <c r="H16" t="n">
         <v>15</v>
       </c>
       <c r="I16" t="n">
-        <v>242</v>
+        <v>208</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0391105188183906</v>
+        <v>0.01173802591311461</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0.3521407773934382</v>
       </c>
       <c r="L16" t="b">
         <v>0</v>
@@ -1088,31 +1100,31 @@
         <v>2011</v>
       </c>
       <c r="C17" t="n">
-        <v>11.29168657034119</v>
+        <v>11.30357071181305</v>
       </c>
       <c r="D17" t="n">
-        <v>3.507956204325269</v>
+        <v>3.52238571189375</v>
       </c>
       <c r="E17" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F17" t="n">
-        <v>13.91335089047403</v>
+        <v>14.07544624458466</v>
       </c>
       <c r="G17" t="n">
-        <v>1.611758899203076</v>
+        <v>1.697731590644409</v>
       </c>
       <c r="H17" t="n">
         <v>15</v>
       </c>
       <c r="I17" t="n">
-        <v>205</v>
+        <v>184</v>
       </c>
       <c r="J17" t="n">
-        <v>0.008312365597504444</v>
+        <v>0.003728180372247974</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2493709679251333</v>
+        <v>0.1118454111674392</v>
       </c>
       <c r="L17" t="b">
         <v>0</v>
@@ -1128,31 +1140,31 @@
         <v>2012</v>
       </c>
       <c r="C18" t="n">
-        <v>10.02757963326554</v>
+        <v>9.915451774075638</v>
       </c>
       <c r="D18" t="n">
-        <v>5.376764758171054</v>
+        <v>5.404797370340246</v>
       </c>
       <c r="E18" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F18" t="n">
-        <v>12.0808304409885</v>
+        <v>11.8408347748662</v>
       </c>
       <c r="G18" t="n">
-        <v>2.456019519571016</v>
+        <v>2.152666335547554</v>
       </c>
       <c r="H18" t="n">
         <v>15</v>
       </c>
       <c r="I18" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="J18" t="n">
-        <v>0.02985475370982584</v>
+        <v>0.03787882334931163</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8956426112947753</v>
+        <v>1</v>
       </c>
       <c r="L18" t="b">
         <v>0</v>
@@ -1168,28 +1180,28 @@
         <v>2013</v>
       </c>
       <c r="C19" t="n">
-        <v>9.961875121334387</v>
+        <v>9.931164643712574</v>
       </c>
       <c r="D19" t="n">
-        <v>5.65786371798532</v>
+        <v>5.762848308996083</v>
       </c>
       <c r="E19" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F19" t="n">
-        <v>9.735257139211047</v>
+        <v>9.501805968234342</v>
       </c>
       <c r="G19" t="n">
-        <v>2.727432672940793</v>
+        <v>2.899776460813349</v>
       </c>
       <c r="H19" t="n">
         <v>15</v>
       </c>
       <c r="I19" t="n">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4136862269931683</v>
+        <v>0.3747988343539521</v>
       </c>
       <c r="K19" t="n">
         <v>1</v>
@@ -1208,34 +1220,34 @@
         <v>2014</v>
       </c>
       <c r="C20" t="n">
-        <v>10.42242663546237</v>
+        <v>10.35448975104345</v>
       </c>
       <c r="D20" t="n">
-        <v>3.11095421913185</v>
+        <v>3.005848310776555</v>
       </c>
       <c r="E20" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F20" t="n">
-        <v>13.58724591922996</v>
+        <v>13.28203084925863</v>
       </c>
       <c r="G20" t="n">
-        <v>2.659882438433262</v>
+        <v>2.584606915807451</v>
       </c>
       <c r="H20" t="n">
         <v>15</v>
       </c>
       <c r="I20" t="n">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="J20" t="n">
-        <v>0.001616456990401316</v>
+        <v>0.003543935133297633</v>
       </c>
       <c r="K20" t="n">
-        <v>0.04849370971203949</v>
+        <v>0.106318053998929</v>
       </c>
       <c r="L20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1248,28 +1260,28 @@
         <v>2015</v>
       </c>
       <c r="C21" t="n">
-        <v>9.639281969704562</v>
+        <v>9.566405787436976</v>
       </c>
       <c r="D21" t="n">
-        <v>4.172817458572816</v>
+        <v>4.302198587632208</v>
       </c>
       <c r="E21" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F21" t="n">
-        <v>10.87258311582019</v>
+        <v>10.77392519488214</v>
       </c>
       <c r="G21" t="n">
-        <v>2.070302054545978</v>
+        <v>1.943065569977875</v>
       </c>
       <c r="H21" t="n">
         <v>15</v>
       </c>
       <c r="I21" t="n">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3152515554041375</v>
+        <v>0.3579818361905036</v>
       </c>
       <c r="K21" t="n">
         <v>1</v>
@@ -1288,31 +1300,31 @@
         <v>2016</v>
       </c>
       <c r="C22" t="n">
-        <v>9.380907318272612</v>
+        <v>9.224354498586436</v>
       </c>
       <c r="D22" t="n">
-        <v>3.690909216636495</v>
+        <v>3.756024254384788</v>
       </c>
       <c r="E22" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F22" t="n">
-        <v>13.54482598076801</v>
+        <v>13.37371161401667</v>
       </c>
       <c r="G22" t="n">
-        <v>1.796249736256293</v>
+        <v>1.977761419189816</v>
       </c>
       <c r="H22" t="n">
         <v>15</v>
       </c>
       <c r="I22" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0002311391795674252</v>
+        <v>0.0003412631980929644</v>
       </c>
       <c r="K22" t="n">
-        <v>0.006934175387022756</v>
+        <v>0.01023789594278893</v>
       </c>
       <c r="L22" t="b">
         <v>1</v>
@@ -1328,34 +1340,34 @@
         <v>2017</v>
       </c>
       <c r="C23" t="n">
-        <v>9.054283479096281</v>
+        <v>9.016123623434025</v>
       </c>
       <c r="D23" t="n">
-        <v>4.048434926590839</v>
+        <v>4.103469192377825</v>
       </c>
       <c r="E23" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F23" t="n">
-        <v>12.14289940743063</v>
+        <v>12.2565562442287</v>
       </c>
       <c r="G23" t="n">
-        <v>1.654269773517323</v>
+        <v>1.530067486436928</v>
       </c>
       <c r="H23" t="n">
         <v>15</v>
       </c>
       <c r="I23" t="n">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="J23" t="n">
-        <v>0.001895015795562726</v>
+        <v>0.001444721528280682</v>
       </c>
       <c r="K23" t="n">
-        <v>0.05685047386688177</v>
+        <v>0.04334164584842047</v>
       </c>
       <c r="L23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1368,28 +1380,28 @@
         <v>2018</v>
       </c>
       <c r="C24" t="n">
-        <v>13.15656428192963</v>
+        <v>13.08385280562495</v>
       </c>
       <c r="D24" t="n">
-        <v>3.26326998224749</v>
+        <v>3.489944582503852</v>
       </c>
       <c r="E24" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F24" t="n">
-        <v>12.37700444959472</v>
+        <v>11.69219167281753</v>
       </c>
       <c r="G24" t="n">
-        <v>5.344469283756904</v>
+        <v>4.924838516772379</v>
       </c>
       <c r="H24" t="n">
         <v>15</v>
       </c>
       <c r="I24" t="n">
-        <v>450</v>
+        <v>484</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2460636969324763</v>
+        <v>0.06599834109292449</v>
       </c>
       <c r="K24" t="n">
         <v>1</v>
@@ -1408,31 +1420,31 @@
         <v>2019</v>
       </c>
       <c r="C25" t="n">
-        <v>9.285615189331503</v>
+        <v>9.158508517052985</v>
       </c>
       <c r="D25" t="n">
-        <v>3.660912271088988</v>
+        <v>3.758842015222396</v>
       </c>
       <c r="E25" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F25" t="n">
-        <v>12.9342454757541</v>
+        <v>12.86763447208676</v>
       </c>
       <c r="G25" t="n">
-        <v>2.424356392911593</v>
+        <v>2.527957525019283</v>
       </c>
       <c r="H25" t="n">
         <v>15</v>
       </c>
       <c r="I25" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0004732449202420883</v>
+        <v>0.0006186743397443925</v>
       </c>
       <c r="K25" t="n">
-        <v>0.01419734760726265</v>
+        <v>0.01856023019233178</v>
       </c>
       <c r="L25" t="b">
         <v>1</v>
@@ -1448,31 +1460,31 @@
         <v>2020</v>
       </c>
       <c r="C26" t="n">
-        <v>9.714330116561328</v>
+        <v>9.685813903795903</v>
       </c>
       <c r="D26" t="n">
-        <v>3.631475729237351</v>
+        <v>3.586163524041788</v>
       </c>
       <c r="E26" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F26" t="n">
-        <v>12.74776603973598</v>
+        <v>13.03081888860066</v>
       </c>
       <c r="G26" t="n">
-        <v>2.99490039083592</v>
+        <v>3.057503847837081</v>
       </c>
       <c r="H26" t="n">
         <v>15</v>
       </c>
       <c r="I26" t="n">
-        <v>207</v>
+        <v>183</v>
       </c>
       <c r="J26" t="n">
-        <v>0.009108054720018657</v>
+        <v>0.003543935133297633</v>
       </c>
       <c r="K26" t="n">
-        <v>0.2732416416005597</v>
+        <v>0.106318053998929</v>
       </c>
       <c r="L26" t="b">
         <v>0</v>
@@ -1488,31 +1500,31 @@
         <v>2021</v>
       </c>
       <c r="C27" t="n">
-        <v>7.640942534158182</v>
+        <v>7.541755630463211</v>
       </c>
       <c r="D27" t="n">
-        <v>4.460072202618072</v>
+        <v>4.452141266873435</v>
       </c>
       <c r="E27" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F27" t="n">
-        <v>13.24775158900663</v>
+        <v>13.49066310856644</v>
       </c>
       <c r="G27" t="n">
-        <v>2.447363634919084</v>
+        <v>2.540766221583837</v>
       </c>
       <c r="H27" t="n">
         <v>15</v>
       </c>
       <c r="I27" t="n">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="J27" t="n">
-        <v>2.059052102158814e-05</v>
+        <v>1.626554502992606e-05</v>
       </c>
       <c r="K27" t="n">
-        <v>0.000617715630647644</v>
+        <v>0.0004879663508977816</v>
       </c>
       <c r="L27" t="b">
         <v>1</v>
@@ -1528,28 +1540,28 @@
         <v>2022</v>
       </c>
       <c r="C28" t="n">
-        <v>9.908177549508432</v>
+        <v>9.714891774804881</v>
       </c>
       <c r="D28" t="n">
-        <v>4.914015731778095</v>
+        <v>4.901517315538166</v>
       </c>
       <c r="E28" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F28" t="n">
-        <v>9.752439601695096</v>
+        <v>9.906308974334198</v>
       </c>
       <c r="G28" t="n">
-        <v>1.419129687317649</v>
+        <v>1.440617205495534</v>
       </c>
       <c r="H28" t="n">
         <v>15</v>
       </c>
       <c r="I28" t="n">
-        <v>393</v>
+        <v>368</v>
       </c>
       <c r="J28" t="n">
-        <v>0.7852570955409328</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
@@ -1568,31 +1580,31 @@
         <v>2023</v>
       </c>
       <c r="C29" t="n">
-        <v>8.820998721770577</v>
+        <v>8.714333644651907</v>
       </c>
       <c r="D29" t="n">
-        <v>3.665957062873648</v>
+        <v>3.615694980935317</v>
       </c>
       <c r="E29" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F29" t="n">
-        <v>16.29619665720363</v>
+        <v>16.19165461848831</v>
       </c>
       <c r="G29" t="n">
-        <v>2.529568367102435</v>
+        <v>2.422873002156922</v>
       </c>
       <c r="H29" t="n">
         <v>15</v>
       </c>
       <c r="I29" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="J29" t="n">
-        <v>1.054064530485306e-07</v>
+        <v>8.469987578433327e-08</v>
       </c>
       <c r="K29" t="n">
-        <v>3.162193591455917e-06</v>
+        <v>2.540996273529998e-06</v>
       </c>
       <c r="L29" t="b">
         <v>1</v>
@@ -1608,28 +1620,28 @@
         <v>2024</v>
       </c>
       <c r="C30" t="n">
-        <v>12.29842330189011</v>
+        <v>12.16612046154192</v>
       </c>
       <c r="D30" t="n">
-        <v>4.963775024259399</v>
+        <v>4.968189555810989</v>
       </c>
       <c r="E30" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F30" t="n">
-        <v>13.59360065076396</v>
+        <v>13.11743712165599</v>
       </c>
       <c r="G30" t="n">
-        <v>2.876912891702416</v>
+        <v>2.958160741088972</v>
       </c>
       <c r="H30" t="n">
         <v>15</v>
       </c>
       <c r="I30" t="n">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="J30" t="n">
-        <v>0.4786757603358271</v>
+        <v>0.6572159973411411</v>
       </c>
       <c r="K30" t="n">
         <v>1</v>
@@ -1648,28 +1660,28 @@
         <v>2025</v>
       </c>
       <c r="C31" t="n">
-        <v>10.50954144330246</v>
+        <v>10.47940308441554</v>
       </c>
       <c r="D31" t="n">
-        <v>3.450269510209733</v>
+        <v>3.421051648572962</v>
       </c>
       <c r="E31" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F31" t="n">
-        <v>12.18305748970569</v>
+        <v>11.49743937397262</v>
       </c>
       <c r="G31" t="n">
-        <v>4.832737270102345</v>
+        <v>4.831287020020368</v>
       </c>
       <c r="H31" t="n">
         <v>15</v>
       </c>
       <c r="I31" t="n">
-        <v>322</v>
+        <v>357</v>
       </c>
       <c r="J31" t="n">
-        <v>0.4136862269931683</v>
+        <v>0.8740740325709885</v>
       </c>
       <c r="K31" t="n">
         <v>1</v>
@@ -1688,31 +1700,31 @@
         <v>1996</v>
       </c>
       <c r="C32" t="n">
-        <v>74.87485895567022</v>
+        <v>75.02143654959377</v>
       </c>
       <c r="D32" t="n">
-        <v>16.09865736271095</v>
+        <v>16.31032227147226</v>
       </c>
       <c r="E32" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F32" t="n">
-        <v>85.57103864950233</v>
+        <v>85.22457150055298</v>
       </c>
       <c r="G32" t="n">
-        <v>6.436375240983608</v>
+        <v>6.588474141795251</v>
       </c>
       <c r="H32" t="n">
         <v>15</v>
       </c>
       <c r="I32" t="n">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="J32" t="n">
-        <v>0.02870006176440242</v>
+        <v>0.05125066078073648</v>
       </c>
       <c r="K32" t="n">
-        <v>0.8610018529320724</v>
+        <v>1</v>
       </c>
       <c r="L32" t="b">
         <v>0</v>
@@ -1728,31 +1740,31 @@
         <v>1997</v>
       </c>
       <c r="C33" t="n">
-        <v>71.12978765718378</v>
+        <v>70.96754063676569</v>
       </c>
       <c r="D33" t="n">
-        <v>10.01972727083556</v>
+        <v>9.857985459922974</v>
       </c>
       <c r="E33" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F33" t="n">
-        <v>76.10844796414828</v>
+        <v>76.37848519798492</v>
       </c>
       <c r="G33" t="n">
-        <v>5.040159438983236</v>
+        <v>5.134037909774356</v>
       </c>
       <c r="H33" t="n">
         <v>15</v>
       </c>
       <c r="I33" t="n">
-        <v>247</v>
+        <v>228</v>
       </c>
       <c r="J33" t="n">
-        <v>0.04712530418391234</v>
+        <v>0.02759811731132039</v>
       </c>
       <c r="K33" t="n">
-        <v>1</v>
+        <v>0.8279435193396117</v>
       </c>
       <c r="L33" t="b">
         <v>0</v>
@@ -1768,31 +1780,31 @@
         <v>1998</v>
       </c>
       <c r="C34" t="n">
-        <v>69.1232247342019</v>
+        <v>69.47497990123492</v>
       </c>
       <c r="D34" t="n">
-        <v>9.223116267244176</v>
+        <v>9.227494338192333</v>
       </c>
       <c r="E34" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F34" t="n">
-        <v>84.30282638452627</v>
+        <v>84.69567609760203</v>
       </c>
       <c r="G34" t="n">
-        <v>3.647815580671829</v>
+        <v>4.275753559495218</v>
       </c>
       <c r="H34" t="n">
         <v>15</v>
       </c>
       <c r="I34" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J34" t="n">
-        <v>1.334951691917815e-06</v>
+        <v>1.450280451936633e-06</v>
       </c>
       <c r="K34" t="n">
-        <v>4.004855075753445e-05</v>
+        <v>4.350841355809898e-05</v>
       </c>
       <c r="L34" t="b">
         <v>1</v>
@@ -1808,31 +1820,31 @@
         <v>1999</v>
       </c>
       <c r="C35" t="n">
-        <v>71.88149109497364</v>
+        <v>71.62485567406786</v>
       </c>
       <c r="D35" t="n">
-        <v>11.03080812091101</v>
+        <v>11.2441107697242</v>
       </c>
       <c r="E35" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F35" t="n">
-        <v>78.23943404375905</v>
+        <v>78.49047612080282</v>
       </c>
       <c r="G35" t="n">
-        <v>6.307108511171172</v>
+        <v>6.445297274521465</v>
       </c>
       <c r="H35" t="n">
         <v>15</v>
       </c>
       <c r="I35" t="n">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="J35" t="n">
-        <v>0.03228435391076682</v>
+        <v>0.02343017548881787</v>
       </c>
       <c r="K35" t="n">
-        <v>0.9685306173230047</v>
+        <v>0.7029052646645361</v>
       </c>
       <c r="L35" t="b">
         <v>0</v>
@@ -1848,34 +1860,34 @@
         <v>2000</v>
       </c>
       <c r="C36" t="n">
-        <v>67.53981698993931</v>
+        <v>66.90493064611418</v>
       </c>
       <c r="D36" t="n">
-        <v>12.15923638400224</v>
+        <v>11.58475329873503</v>
       </c>
       <c r="E36" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F36" t="n">
-        <v>78.10303629720259</v>
+        <v>78.32146469632238</v>
       </c>
       <c r="G36" t="n">
-        <v>6.683149746951404</v>
+        <v>6.867551868853835</v>
       </c>
       <c r="H36" t="n">
         <v>15</v>
       </c>
       <c r="I36" t="n">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="J36" t="n">
-        <v>0.003016210616723252</v>
+        <v>0.0009251486324161695</v>
       </c>
       <c r="K36" t="n">
-        <v>0.09048631850169755</v>
+        <v>0.02775445897248509</v>
       </c>
       <c r="L36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -1888,31 +1900,31 @@
         <v>2001</v>
       </c>
       <c r="C37" t="n">
-        <v>74.82849417510512</v>
+        <v>74.4335007484287</v>
       </c>
       <c r="D37" t="n">
-        <v>11.21687695493018</v>
+        <v>11.10781949440094</v>
       </c>
       <c r="E37" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F37" t="n">
-        <v>86.41390427328156</v>
+        <v>85.67821966750948</v>
       </c>
       <c r="G37" t="n">
-        <v>6.61826158995902</v>
+        <v>6.784838361849604</v>
       </c>
       <c r="H37" t="n">
         <v>15</v>
       </c>
       <c r="I37" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="J37" t="n">
-        <v>0.0004463736208085871</v>
+        <v>0.0006186743397443925</v>
       </c>
       <c r="K37" t="n">
-        <v>0.01339120862425761</v>
+        <v>0.01856023019233178</v>
       </c>
       <c r="L37" t="b">
         <v>1</v>
@@ -1928,31 +1940,31 @@
         <v>2002</v>
       </c>
       <c r="C38" t="n">
-        <v>73.46678411360826</v>
+        <v>74.12259946070623</v>
       </c>
       <c r="D38" t="n">
-        <v>11.93868818116675</v>
+        <v>11.90840216801012</v>
       </c>
       <c r="E38" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F38" t="n">
-        <v>82.7890220534313</v>
+        <v>83.02660248059618</v>
       </c>
       <c r="G38" t="n">
-        <v>5.650980725699082</v>
+        <v>5.636875002219917</v>
       </c>
       <c r="H38" t="n">
         <v>15</v>
       </c>
       <c r="I38" t="n">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="J38" t="n">
-        <v>0.005715509149697121</v>
+        <v>0.01072231151822285</v>
       </c>
       <c r="K38" t="n">
-        <v>0.1714652744909136</v>
+        <v>0.3216693455466854</v>
       </c>
       <c r="L38" t="b">
         <v>0</v>
@@ -1968,28 +1980,28 @@
         <v>2003</v>
       </c>
       <c r="C39" t="n">
-        <v>66.02711386611874</v>
+        <v>65.60664945353126</v>
       </c>
       <c r="D39" t="n">
-        <v>11.1098976608008</v>
+        <v>11.51286084142742</v>
       </c>
       <c r="E39" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F39" t="n">
-        <v>68.51798121329122</v>
+        <v>70.42892210781142</v>
       </c>
       <c r="G39" t="n">
-        <v>9.955538772906683</v>
+        <v>11.18093194284582</v>
       </c>
       <c r="H39" t="n">
         <v>15</v>
       </c>
       <c r="I39" t="n">
-        <v>320</v>
+        <v>277</v>
       </c>
       <c r="J39" t="n">
-        <v>0.3961240299869637</v>
+        <v>0.1537610108349084</v>
       </c>
       <c r="K39" t="n">
         <v>1</v>
@@ -2008,31 +2020,31 @@
         <v>2004</v>
       </c>
       <c r="C40" t="n">
-        <v>73.7534181452054</v>
+        <v>73.6151098209867</v>
       </c>
       <c r="D40" t="n">
-        <v>10.26982496751293</v>
+        <v>10.536378015935</v>
       </c>
       <c r="E40" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F40" t="n">
-        <v>81.63153450636338</v>
+        <v>82.96031570161378</v>
       </c>
       <c r="G40" t="n">
-        <v>9.038515084544077</v>
+        <v>7.024269067901884</v>
       </c>
       <c r="H40" t="n">
         <v>15</v>
       </c>
       <c r="I40" t="n">
-        <v>205</v>
+        <v>171</v>
       </c>
       <c r="J40" t="n">
-        <v>0.008312365597504444</v>
+        <v>0.001894308937787045</v>
       </c>
       <c r="K40" t="n">
-        <v>0.2493709679251333</v>
+        <v>0.05682926813361135</v>
       </c>
       <c r="L40" t="b">
         <v>0</v>
@@ -2048,34 +2060,34 @@
         <v>2005</v>
       </c>
       <c r="C41" t="n">
-        <v>69.60877787524764</v>
+        <v>69.26773823114816</v>
       </c>
       <c r="D41" t="n">
-        <v>11.31652853742648</v>
+        <v>11.34483966591612</v>
       </c>
       <c r="E41" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F41" t="n">
-        <v>79.47395296622476</v>
+        <v>80.45078194051462</v>
       </c>
       <c r="G41" t="n">
-        <v>6.116028525518993</v>
+        <v>6.852516277636982</v>
       </c>
       <c r="H41" t="n">
         <v>15</v>
       </c>
       <c r="I41" t="n">
-        <v>188</v>
+        <v>164</v>
       </c>
       <c r="J41" t="n">
-        <v>0.003686623316238023</v>
+        <v>0.001294207427246684</v>
       </c>
       <c r="K41" t="n">
-        <v>0.1105986994871407</v>
+        <v>0.03882622281740051</v>
       </c>
       <c r="L41" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2088,28 +2100,28 @@
         <v>2006</v>
       </c>
       <c r="C42" t="n">
-        <v>69.52036440613578</v>
+        <v>69.09786085020934</v>
       </c>
       <c r="D42" t="n">
-        <v>11.18430647115636</v>
+        <v>10.93906818097358</v>
       </c>
       <c r="E42" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F42" t="n">
-        <v>74.81421784293259</v>
+        <v>76.04103091694982</v>
       </c>
       <c r="G42" t="n">
-        <v>9.588583347316845</v>
+        <v>10.56698042388904</v>
       </c>
       <c r="H42" t="n">
         <v>15</v>
       </c>
       <c r="I42" t="n">
-        <v>282</v>
+        <v>246</v>
       </c>
       <c r="J42" t="n">
-        <v>0.1498043048457331</v>
+        <v>0.05515187566714153</v>
       </c>
       <c r="K42" t="n">
         <v>1</v>
@@ -2128,31 +2140,31 @@
         <v>2007</v>
       </c>
       <c r="C43" t="n">
-        <v>61.83874512012444</v>
+        <v>61.47248618858494</v>
       </c>
       <c r="D43" t="n">
-        <v>10.51099563236924</v>
+        <v>10.66919158927454</v>
       </c>
       <c r="E43" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F43" t="n">
-        <v>79.89875489549271</v>
+        <v>79.84464118110289</v>
       </c>
       <c r="G43" t="n">
-        <v>8.812974479615423</v>
+        <v>8.76491751963661</v>
       </c>
       <c r="H43" t="n">
         <v>15</v>
       </c>
       <c r="I43" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J43" t="n">
-        <v>4.8821596046549e-06</v>
+        <v>5.009483315569529e-06</v>
       </c>
       <c r="K43" t="n">
-        <v>0.000146464788139647</v>
+        <v>0.0001502844994670859</v>
       </c>
       <c r="L43" t="b">
         <v>1</v>
@@ -2168,34 +2180,34 @@
         <v>2008</v>
       </c>
       <c r="C44" t="n">
-        <v>73.43510313287157</v>
+        <v>73.75827811190597</v>
       </c>
       <c r="D44" t="n">
-        <v>11.24715506886669</v>
+        <v>10.65778175588904</v>
       </c>
       <c r="E44" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F44" t="n">
-        <v>83.17883591017615</v>
+        <v>83.34179261035615</v>
       </c>
       <c r="G44" t="n">
-        <v>5.711774696969713</v>
+        <v>5.522343976770774</v>
       </c>
       <c r="H44" t="n">
         <v>15</v>
       </c>
       <c r="I44" t="n">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="J44" t="n">
-        <v>0.002866986637901817</v>
+        <v>0.001444721528280682</v>
       </c>
       <c r="K44" t="n">
-        <v>0.08600959913705451</v>
+        <v>0.04334164584842047</v>
       </c>
       <c r="L44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2208,31 +2220,31 @@
         <v>2009</v>
       </c>
       <c r="C45" t="n">
-        <v>68.68227851205982</v>
+        <v>68.21958417837781</v>
       </c>
       <c r="D45" t="n">
-        <v>10.03460292624761</v>
+        <v>9.844447673012883</v>
       </c>
       <c r="E45" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F45" t="n">
-        <v>80.44197112566491</v>
+        <v>80.37815380381466</v>
       </c>
       <c r="G45" t="n">
-        <v>5.103892197225665</v>
+        <v>5.174756861350118</v>
       </c>
       <c r="H45" t="n">
         <v>15</v>
       </c>
       <c r="I45" t="n">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="J45" t="n">
-        <v>6.945950959519601e-05</v>
+        <v>5.313595172512525e-05</v>
       </c>
       <c r="K45" t="n">
-        <v>0.002083785287855881</v>
+        <v>0.001594078551753757</v>
       </c>
       <c r="L45" t="b">
         <v>1</v>
@@ -2248,31 +2260,31 @@
         <v>2010</v>
       </c>
       <c r="C46" t="n">
-        <v>74.29170800358438</v>
+        <v>74.04162406348564</v>
       </c>
       <c r="D46" t="n">
-        <v>12.17339077953895</v>
+        <v>12.46499205094329</v>
       </c>
       <c r="E46" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F46" t="n">
-        <v>83.3569230956535</v>
+        <v>83.69633899025072</v>
       </c>
       <c r="G46" t="n">
-        <v>8.107585391949714</v>
+        <v>7.956718916849129</v>
       </c>
       <c r="H46" t="n">
         <v>15</v>
       </c>
       <c r="I46" t="n">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="J46" t="n">
-        <v>0.005193003141555862</v>
+        <v>0.003921091999007251</v>
       </c>
       <c r="K46" t="n">
-        <v>0.1557900942466759</v>
+        <v>0.1176327599702175</v>
       </c>
       <c r="L46" t="b">
         <v>0</v>
@@ -2288,31 +2300,31 @@
         <v>2011</v>
       </c>
       <c r="C47" t="n">
-        <v>67.36713362150188</v>
+        <v>67.37014681758642</v>
       </c>
       <c r="D47" t="n">
-        <v>10.79311059929371</v>
+        <v>10.70973972649761</v>
       </c>
       <c r="E47" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F47" t="n">
-        <v>79.13019275001292</v>
+        <v>78.04427066342009</v>
       </c>
       <c r="G47" t="n">
-        <v>6.006719697071195</v>
+        <v>4.994906851981915</v>
       </c>
       <c r="H47" t="n">
         <v>15</v>
       </c>
       <c r="I47" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="J47" t="n">
-        <v>0.0002773450677681151</v>
+        <v>0.0004089608878057362</v>
       </c>
       <c r="K47" t="n">
-        <v>0.008320352033043455</v>
+        <v>0.01226882663417209</v>
       </c>
       <c r="L47" t="b">
         <v>1</v>
@@ -2328,31 +2340,31 @@
         <v>2012</v>
       </c>
       <c r="C48" t="n">
-        <v>69.65030606931693</v>
+        <v>69.56081313626287</v>
       </c>
       <c r="D48" t="n">
-        <v>10.7004307604876</v>
+        <v>10.36394314283433</v>
       </c>
       <c r="E48" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F48" t="n">
-        <v>74.77968194998682</v>
+        <v>74.72907036823071</v>
       </c>
       <c r="G48" t="n">
-        <v>3.240569995215182</v>
+        <v>3.284693654579341</v>
       </c>
       <c r="H48" t="n">
         <v>15</v>
       </c>
       <c r="I48" t="n">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="J48" t="n">
-        <v>0.03624553734788172</v>
+        <v>0.02441735419230902</v>
       </c>
       <c r="K48" t="n">
-        <v>1</v>
+        <v>0.7325206257692707</v>
       </c>
       <c r="L48" t="b">
         <v>0</v>
@@ -2368,31 +2380,31 @@
         <v>2013</v>
       </c>
       <c r="C49" t="n">
-        <v>74.9811400242676</v>
+        <v>74.83993766887347</v>
       </c>
       <c r="D49" t="n">
-        <v>10.14154703637963</v>
+        <v>10.12630090430897</v>
       </c>
       <c r="E49" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F49" t="n">
-        <v>82.84949122226412</v>
+        <v>81.32463433552114</v>
       </c>
       <c r="G49" t="n">
-        <v>6.026567460369841</v>
+        <v>7.477685521919232</v>
       </c>
       <c r="H49" t="n">
         <v>15</v>
       </c>
       <c r="I49" t="n">
-        <v>201</v>
+        <v>231</v>
       </c>
       <c r="J49" t="n">
-        <v>0.006905003965885233</v>
+        <v>0.03113003998529647</v>
       </c>
       <c r="K49" t="n">
-        <v>0.207150118976557</v>
+        <v>0.9339011995588942</v>
       </c>
       <c r="L49" t="b">
         <v>0</v>
@@ -2408,31 +2420,31 @@
         <v>2014</v>
       </c>
       <c r="C50" t="n">
-        <v>75.86863298912968</v>
+        <v>75.78990891420217</v>
       </c>
       <c r="D50" t="n">
-        <v>7.781788962276372</v>
+        <v>7.318750148334779</v>
       </c>
       <c r="E50" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F50" t="n">
-        <v>84.72655696266136</v>
+        <v>85.55117274882316</v>
       </c>
       <c r="G50" t="n">
-        <v>5.051867871371076</v>
+        <v>4.504708638099302</v>
       </c>
       <c r="H50" t="n">
         <v>15</v>
       </c>
       <c r="I50" t="n">
-        <v>123</v>
+        <v>85</v>
       </c>
       <c r="J50" t="n">
-        <v>9.00863643856539e-05</v>
+        <v>7.847646676741527e-06</v>
       </c>
       <c r="K50" t="n">
-        <v>0.002702590931569617</v>
+        <v>0.0002354294003022458</v>
       </c>
       <c r="L50" t="b">
         <v>1</v>
@@ -2448,31 +2460,31 @@
         <v>2015</v>
       </c>
       <c r="C51" t="n">
-        <v>68.61662680863088</v>
+        <v>68.81104537804367</v>
       </c>
       <c r="D51" t="n">
-        <v>8.370047554063925</v>
+        <v>8.556700207081523</v>
       </c>
       <c r="E51" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F51" t="n">
-        <v>79.76048698336224</v>
+        <v>79.36799800187573</v>
       </c>
       <c r="G51" t="n">
-        <v>4.519564957285721</v>
+        <v>4.85057063797078</v>
       </c>
       <c r="H51" t="n">
         <v>15</v>
       </c>
       <c r="I51" t="n">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="J51" t="n">
-        <v>1.449412669232289e-05</v>
+        <v>5.684506238955547e-05</v>
       </c>
       <c r="K51" t="n">
-        <v>0.0004348238007696868</v>
+        <v>0.001705351871686664</v>
       </c>
       <c r="L51" t="b">
         <v>1</v>
@@ -2488,31 +2500,31 @@
         <v>2016</v>
       </c>
       <c r="C52" t="n">
-        <v>71.15950225315898</v>
+        <v>71.40156962893289</v>
       </c>
       <c r="D52" t="n">
-        <v>9.206414887138887</v>
+        <v>9.390228556049058</v>
       </c>
       <c r="E52" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F52" t="n">
-        <v>79.31910332898639</v>
+        <v>79.34352970107015</v>
       </c>
       <c r="G52" t="n">
-        <v>6.44000441552511</v>
+        <v>6.486565914482826</v>
       </c>
       <c r="H52" t="n">
         <v>15</v>
       </c>
       <c r="I52" t="n">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="J52" t="n">
-        <v>0.002724531790919405</v>
+        <v>0.003728180372247974</v>
       </c>
       <c r="K52" t="n">
-        <v>0.08173595372758215</v>
+        <v>0.1118454111674392</v>
       </c>
       <c r="L52" t="b">
         <v>0</v>
@@ -2528,31 +2540,31 @@
         <v>2017</v>
       </c>
       <c r="C53" t="n">
-        <v>74.90695492231636</v>
+        <v>74.8059465247397</v>
       </c>
       <c r="D53" t="n">
-        <v>9.575825822916878</v>
+        <v>9.657774726231493</v>
       </c>
       <c r="E53" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F53" t="n">
-        <v>83.9254805392446</v>
+        <v>84.35097103933172</v>
       </c>
       <c r="G53" t="n">
-        <v>5.730572107723947</v>
+        <v>5.754151333276585</v>
       </c>
       <c r="H53" t="n">
         <v>15</v>
       </c>
       <c r="I53" t="n">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="J53" t="n">
-        <v>0.0007927023228354832</v>
+        <v>0.0004890434469947135</v>
       </c>
       <c r="K53" t="n">
-        <v>0.0237810696850645</v>
+        <v>0.0146713034098414</v>
       </c>
       <c r="L53" t="b">
         <v>1</v>
@@ -2568,28 +2580,28 @@
         <v>2018</v>
       </c>
       <c r="C54" t="n">
-        <v>67.74311530136168</v>
+        <v>68.18016778664067</v>
       </c>
       <c r="D54" t="n">
-        <v>9.743648173682674</v>
+        <v>9.907903657752787</v>
       </c>
       <c r="E54" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F54" t="n">
-        <v>67.47103115070135</v>
+        <v>68.35031873699832</v>
       </c>
       <c r="G54" t="n">
-        <v>9.671099375340976</v>
+        <v>9.168976226692248</v>
       </c>
       <c r="H54" t="n">
         <v>15</v>
       </c>
       <c r="I54" t="n">
-        <v>393</v>
+        <v>369</v>
       </c>
       <c r="J54" t="n">
-        <v>0.7852570955409328</v>
+        <v>0.9873551944235081</v>
       </c>
       <c r="K54" t="n">
         <v>1</v>
@@ -2608,31 +2620,31 @@
         <v>2019</v>
       </c>
       <c r="C55" t="n">
-        <v>67.97775193465634</v>
+        <v>67.29575129379253</v>
       </c>
       <c r="D55" t="n">
-        <v>11.45303156962887</v>
+        <v>11.40479429364223</v>
       </c>
       <c r="E55" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F55" t="n">
-        <v>75.60051330755179</v>
+        <v>76.45809555122787</v>
       </c>
       <c r="G55" t="n">
-        <v>8.451786595629063</v>
+        <v>8.746020608145178</v>
       </c>
       <c r="H55" t="n">
         <v>15</v>
       </c>
       <c r="I55" t="n">
-        <v>216</v>
+        <v>190</v>
       </c>
       <c r="J55" t="n">
-        <v>0.01359304350332968</v>
+        <v>0.005028565822497875</v>
       </c>
       <c r="K55" t="n">
-        <v>0.4077913050998905</v>
+        <v>0.1508569746749363</v>
       </c>
       <c r="L55" t="b">
         <v>0</v>
@@ -2648,31 +2660,31 @@
         <v>2020</v>
       </c>
       <c r="C56" t="n">
-        <v>61.26100123816903</v>
+        <v>61.03680486988018</v>
       </c>
       <c r="D56" t="n">
-        <v>10.2735051472748</v>
+        <v>10.30919292973285</v>
       </c>
       <c r="E56" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F56" t="n">
-        <v>75.27954677345504</v>
+        <v>76.37768132318077</v>
       </c>
       <c r="G56" t="n">
-        <v>10.40225230769028</v>
+        <v>9.718007730911198</v>
       </c>
       <c r="H56" t="n">
         <v>15</v>
       </c>
       <c r="I56" t="n">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="J56" t="n">
-        <v>0.0001407424567195696</v>
+        <v>3.070471405943822e-05</v>
       </c>
       <c r="K56" t="n">
-        <v>0.004222273701587089</v>
+        <v>0.0009211414217831467</v>
       </c>
       <c r="L56" t="b">
         <v>1</v>
@@ -2688,31 +2700,31 @@
         <v>2021</v>
       </c>
       <c r="C57" t="n">
-        <v>71.90223247459303</v>
+        <v>72.11029345432868</v>
       </c>
       <c r="D57" t="n">
-        <v>11.90158305297044</v>
+        <v>11.78580444708732</v>
       </c>
       <c r="E57" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F57" t="n">
-        <v>79.36015769235385</v>
+        <v>77.72131179212892</v>
       </c>
       <c r="G57" t="n">
-        <v>6.987718652185899</v>
+        <v>7.329139623972533</v>
       </c>
       <c r="H57" t="n">
         <v>15</v>
       </c>
       <c r="I57" t="n">
-        <v>227</v>
+        <v>259</v>
       </c>
       <c r="J57" t="n">
-        <v>0.02164320401389676</v>
+        <v>0.08696186670619793</v>
       </c>
       <c r="K57" t="n">
-        <v>0.6492961204169029</v>
+        <v>1</v>
       </c>
       <c r="L57" t="b">
         <v>0</v>
@@ -2728,31 +2740,31 @@
         <v>2022</v>
       </c>
       <c r="C58" t="n">
-        <v>69.06205893411459</v>
+        <v>68.25564324795592</v>
       </c>
       <c r="D58" t="n">
-        <v>10.13541585079147</v>
+        <v>10.20299556099853</v>
       </c>
       <c r="E58" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F58" t="n">
-        <v>82.45159488148354</v>
+        <v>82.38634836854716</v>
       </c>
       <c r="G58" t="n">
-        <v>4.587063040980997</v>
+        <v>4.555975661314735</v>
       </c>
       <c r="H58" t="n">
         <v>15</v>
       </c>
       <c r="I58" t="n">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="J58" t="n">
-        <v>4.992463856937452e-05</v>
+        <v>2.32065676251805e-05</v>
       </c>
       <c r="K58" t="n">
-        <v>0.001497739157081236</v>
+        <v>0.0006961970287554149</v>
       </c>
       <c r="L58" t="b">
         <v>1</v>
@@ -2768,28 +2780,28 @@
         <v>2023</v>
       </c>
       <c r="C59" t="n">
-        <v>73.13040360545114</v>
+        <v>73.35503431000537</v>
       </c>
       <c r="D59" t="n">
-        <v>10.40654239338775</v>
+        <v>10.54486562001677</v>
       </c>
       <c r="E59" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F59" t="n">
-        <v>71.80842476698541</v>
+        <v>71.56381694146525</v>
       </c>
       <c r="G59" t="n">
-        <v>5.899550386812188</v>
+        <v>5.93462885936017</v>
       </c>
       <c r="H59" t="n">
         <v>15</v>
       </c>
       <c r="I59" t="n">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="J59" t="n">
-        <v>0.9070384808036948</v>
+        <v>0.7512651968617754</v>
       </c>
       <c r="K59" t="n">
         <v>1</v>
@@ -2808,31 +2820,31 @@
         <v>2024</v>
       </c>
       <c r="C60" t="n">
-        <v>67.22181351523756</v>
+        <v>67.3790243244794</v>
       </c>
       <c r="D60" t="n">
-        <v>10.29949975161288</v>
+        <v>10.19849891589025</v>
       </c>
       <c r="E60" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F60" t="n">
-        <v>76.51592610222335</v>
+        <v>77.49564671249934</v>
       </c>
       <c r="G60" t="n">
-        <v>6.973298586689892</v>
+        <v>8.078024793223268</v>
       </c>
       <c r="H60" t="n">
         <v>15</v>
       </c>
       <c r="I60" t="n">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="J60" t="n">
-        <v>0.003016210616723252</v>
+        <v>0.002342893238365735</v>
       </c>
       <c r="K60" t="n">
-        <v>0.09048631850169755</v>
+        <v>0.07028679715097204</v>
       </c>
       <c r="L60" t="b">
         <v>0</v>
@@ -2848,31 +2860,31 @@
         <v>2025</v>
       </c>
       <c r="C61" t="n">
-        <v>68.86705083568241</v>
+        <v>68.68560335160741</v>
       </c>
       <c r="D61" t="n">
-        <v>10.23660598004327</v>
+        <v>10.25418613013906</v>
       </c>
       <c r="E61" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F61" t="n">
-        <v>78.42891191918116</v>
+        <v>78.45087569785599</v>
       </c>
       <c r="G61" t="n">
-        <v>7.887742295534371</v>
+        <v>7.884826783457468</v>
       </c>
       <c r="H61" t="n">
         <v>15</v>
       </c>
       <c r="I61" t="n">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="J61" t="n">
-        <v>0.001303533771068182</v>
+        <v>0.0009789621246277804</v>
       </c>
       <c r="K61" t="n">
-        <v>0.03910601313204547</v>
+        <v>0.02936886373883341</v>
       </c>
       <c r="L61" t="b">
         <v>1</v>
@@ -2888,28 +2900,28 @@
         <v>1996</v>
       </c>
       <c r="C62" t="n">
-        <v>97.17176020379247</v>
+        <v>96.74456396541035</v>
       </c>
       <c r="D62" t="n">
-        <v>20.79005795894264</v>
+        <v>20.86644082764034</v>
       </c>
       <c r="E62" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F62" t="n">
-        <v>101.5525313708837</v>
+        <v>101.9318799886778</v>
       </c>
       <c r="G62" t="n">
-        <v>7.653661557775169</v>
+        <v>7.490981110730774</v>
       </c>
       <c r="H62" t="n">
         <v>15</v>
       </c>
       <c r="I62" t="n">
-        <v>397</v>
+        <v>378</v>
       </c>
       <c r="J62" t="n">
-        <v>0.7378102511308395</v>
+        <v>0.8740740325709885</v>
       </c>
       <c r="K62" t="n">
         <v>1</v>
@@ -2928,31 +2940,31 @@
         <v>1997</v>
       </c>
       <c r="C63" t="n">
-        <v>105.6769222756861</v>
+        <v>105.6043758845172</v>
       </c>
       <c r="D63" t="n">
-        <v>13.3395785894356</v>
+        <v>13.44265106135083</v>
       </c>
       <c r="E63" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F63" t="n">
-        <v>34.21300952920083</v>
+        <v>34.88370676478908</v>
       </c>
       <c r="G63" t="n">
-        <v>6.841496414890782</v>
+        <v>7.983015078817975</v>
       </c>
       <c r="H63" t="n">
         <v>15</v>
       </c>
       <c r="I63" t="n">
-        <v>750</v>
+        <v>735</v>
       </c>
       <c r="J63" t="n">
-        <v>5.511035590176166e-09</v>
+        <v>6.011850146538538e-09</v>
       </c>
       <c r="K63" t="n">
-        <v>1.65331067705285e-07</v>
+        <v>1.803555043961561e-07</v>
       </c>
       <c r="L63" t="b">
         <v>1</v>
@@ -2968,31 +2980,31 @@
         <v>1998</v>
       </c>
       <c r="C64" t="n">
-        <v>84.98418579111221</v>
+        <v>85.8939117475463</v>
       </c>
       <c r="D64" t="n">
-        <v>22.93877108929608</v>
+        <v>22.30810578247382</v>
       </c>
       <c r="E64" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F64" t="n">
-        <v>104.2866644023018</v>
+        <v>103.8242449287666</v>
       </c>
       <c r="G64" t="n">
-        <v>12.17405798476658</v>
+        <v>11.42567226471773</v>
       </c>
       <c r="H64" t="n">
         <v>15</v>
       </c>
       <c r="I64" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="J64" t="n">
-        <v>0.002866986637901817</v>
+        <v>0.003921091999007251</v>
       </c>
       <c r="K64" t="n">
-        <v>0.08600959913705451</v>
+        <v>0.1176327599702175</v>
       </c>
       <c r="L64" t="b">
         <v>0</v>
@@ -3008,31 +3020,31 @@
         <v>1999</v>
       </c>
       <c r="C65" t="n">
-        <v>101.9155632040755</v>
+        <v>101.7643384531845</v>
       </c>
       <c r="D65" t="n">
-        <v>14.08435415739037</v>
+        <v>14.33646435482303</v>
       </c>
       <c r="E65" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F65" t="n">
-        <v>50.74100651004808</v>
+        <v>53.06498839513158</v>
       </c>
       <c r="G65" t="n">
-        <v>10.64275432695683</v>
+        <v>11.66027971930259</v>
       </c>
       <c r="H65" t="n">
         <v>15</v>
       </c>
       <c r="I65" t="n">
-        <v>748</v>
+        <v>730</v>
       </c>
       <c r="J65" t="n">
-        <v>6.638727483551793e-09</v>
+        <v>9.626315485961566e-09</v>
       </c>
       <c r="K65" t="n">
-        <v>1.991618245065538e-07</v>
+        <v>2.88789464578847e-07</v>
       </c>
       <c r="L65" t="b">
         <v>1</v>
@@ -3048,28 +3060,28 @@
         <v>2000</v>
       </c>
       <c r="C66" t="n">
-        <v>80.38690302858735</v>
+        <v>80.25573155727027</v>
       </c>
       <c r="D66" t="n">
-        <v>26.38604422755019</v>
+        <v>26.26144542803269</v>
       </c>
       <c r="E66" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F66" t="n">
-        <v>76.79239966034528</v>
+        <v>77.44906953486174</v>
       </c>
       <c r="G66" t="n">
-        <v>10.26404913247018</v>
+        <v>10.85227251184012</v>
       </c>
       <c r="H66" t="n">
         <v>15</v>
       </c>
       <c r="I66" t="n">
-        <v>396</v>
+        <v>385</v>
       </c>
       <c r="J66" t="n">
-        <v>0.7495865590587008</v>
+        <v>0.7876020270416147</v>
       </c>
       <c r="K66" t="n">
         <v>1</v>
@@ -3088,28 +3100,28 @@
         <v>2001</v>
       </c>
       <c r="C67" t="n">
-        <v>106.748637418624</v>
+        <v>106.908661772096</v>
       </c>
       <c r="D67" t="n">
-        <v>15.09007966528762</v>
+        <v>14.88180512564135</v>
       </c>
       <c r="E67" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F67" t="n">
-        <v>115.366259835833</v>
+        <v>115.2097156335498</v>
       </c>
       <c r="G67" t="n">
-        <v>5.509481737960042</v>
+        <v>5.565414369359045</v>
       </c>
       <c r="H67" t="n">
         <v>15</v>
       </c>
       <c r="I67" t="n">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="J67" t="n">
-        <v>0.100458935912733</v>
+        <v>0.10944198945514</v>
       </c>
       <c r="K67" t="n">
         <v>1</v>
@@ -3128,28 +3140,28 @@
         <v>2002</v>
       </c>
       <c r="C68" t="n">
-        <v>97.73981941692595</v>
+        <v>98.24832061553728</v>
       </c>
       <c r="D68" t="n">
-        <v>16.26319340999429</v>
+        <v>15.99227533296574</v>
       </c>
       <c r="E68" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F68" t="n">
-        <v>92.02913406925163</v>
+        <v>92.89156826115654</v>
       </c>
       <c r="G68" t="n">
-        <v>13.35268717132875</v>
+        <v>12.84404596408877</v>
       </c>
       <c r="H68" t="n">
         <v>15</v>
       </c>
       <c r="I68" t="n">
-        <v>466</v>
+        <v>459</v>
       </c>
       <c r="J68" t="n">
-        <v>0.1588106007151843</v>
+        <v>0.1492401763148873</v>
       </c>
       <c r="K68" t="n">
         <v>1</v>
@@ -3168,31 +3180,31 @@
         <v>2003</v>
       </c>
       <c r="C69" t="n">
-        <v>80.80093880554764</v>
+        <v>80.6881011108094</v>
       </c>
       <c r="D69" t="n">
-        <v>14.47602548284304</v>
+        <v>14.81515121678728</v>
       </c>
       <c r="E69" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F69" t="n">
-        <v>42.98013246532687</v>
+        <v>42.6696424190961</v>
       </c>
       <c r="G69" t="n">
-        <v>6.119947692706726</v>
+        <v>5.595208862021573</v>
       </c>
       <c r="H69" t="n">
         <v>15</v>
       </c>
       <c r="I69" t="n">
-        <v>738</v>
+        <v>724</v>
       </c>
       <c r="J69" t="n">
-        <v>1.66030808576406e-08</v>
+        <v>1.679948944755923e-08</v>
       </c>
       <c r="K69" t="n">
-        <v>4.980924257292182e-07</v>
+        <v>5.03984683426777e-07</v>
       </c>
       <c r="L69" t="b">
         <v>1</v>
@@ -3208,31 +3220,31 @@
         <v>2004</v>
       </c>
       <c r="C70" t="n">
-        <v>99.04440181149141</v>
+        <v>98.82418745703748</v>
       </c>
       <c r="D70" t="n">
-        <v>16.66377707572002</v>
+        <v>16.83476798168382</v>
       </c>
       <c r="E70" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F70" t="n">
-        <v>71.44990697235579</v>
+        <v>75.81071535050468</v>
       </c>
       <c r="G70" t="n">
-        <v>30.64524662720238</v>
+        <v>27.87750111298218</v>
       </c>
       <c r="H70" t="n">
         <v>15</v>
       </c>
       <c r="I70" t="n">
-        <v>552</v>
+        <v>522</v>
       </c>
       <c r="J70" t="n">
-        <v>0.005994149149114781</v>
+        <v>0.01465960322753029</v>
       </c>
       <c r="K70" t="n">
-        <v>0.1798244744734434</v>
+        <v>0.4397880968259086</v>
       </c>
       <c r="L70" t="b">
         <v>0</v>
@@ -3248,28 +3260,28 @@
         <v>2005</v>
       </c>
       <c r="C71" t="n">
-        <v>87.71352097367664</v>
+        <v>87.12915658196464</v>
       </c>
       <c r="D71" t="n">
-        <v>19.02954846688788</v>
+        <v>18.86331547973484</v>
       </c>
       <c r="E71" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F71" t="n">
-        <v>88.72545787338416</v>
+        <v>89.3248163034247</v>
       </c>
       <c r="G71" t="n">
-        <v>14.31253544351952</v>
+        <v>15.07477208390701</v>
       </c>
       <c r="H71" t="n">
         <v>15</v>
       </c>
       <c r="I71" t="n">
-        <v>342</v>
+        <v>324</v>
       </c>
       <c r="J71" t="n">
-        <v>0.6128395813362166</v>
+        <v>0.495562243322629</v>
       </c>
       <c r="K71" t="n">
         <v>1</v>
@@ -3288,31 +3300,31 @@
         <v>2006</v>
       </c>
       <c r="C72" t="n">
-        <v>93.70025485423126</v>
+        <v>93.84544267749527</v>
       </c>
       <c r="D72" t="n">
-        <v>21.61113876063637</v>
+        <v>21.9638224840284</v>
       </c>
       <c r="E72" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F72" t="n">
-        <v>28.44317426172276</v>
+        <v>33.59519275403332</v>
       </c>
       <c r="G72" t="n">
-        <v>11.61482723666894</v>
+        <v>21.98927150170177</v>
       </c>
       <c r="H72" t="n">
         <v>15</v>
       </c>
       <c r="I72" t="n">
-        <v>743</v>
+        <v>698</v>
       </c>
       <c r="J72" t="n">
-        <v>1.052976152773742e-08</v>
+        <v>1.694821476842483e-07</v>
       </c>
       <c r="K72" t="n">
-        <v>3.158928458321225e-07</v>
+        <v>5.08446443052745e-06</v>
       </c>
       <c r="L72" t="b">
         <v>1</v>
@@ -3328,31 +3340,31 @@
         <v>2007</v>
       </c>
       <c r="C73" t="n">
-        <v>64.11238743277657</v>
+        <v>63.3028284917136</v>
       </c>
       <c r="D73" t="n">
-        <v>29.50794629486074</v>
+        <v>29.22999118400458</v>
       </c>
       <c r="E73" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F73" t="n">
-        <v>103.8080932163409</v>
+        <v>104.0038909331066</v>
       </c>
       <c r="G73" t="n">
-        <v>18.73900870036378</v>
+        <v>18.80863146519038</v>
       </c>
       <c r="H73" t="n">
         <v>15</v>
       </c>
       <c r="I73" t="n">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="J73" t="n">
-        <v>3.817448272469183e-05</v>
+        <v>2.86393430340628e-05</v>
       </c>
       <c r="K73" t="n">
-        <v>0.001145234481740755</v>
+        <v>0.0008591802910218839</v>
       </c>
       <c r="L73" t="b">
         <v>1</v>
@@ -3368,31 +3380,31 @@
         <v>2008</v>
       </c>
       <c r="C74" t="n">
-        <v>102.1420703085194</v>
+        <v>102.5170443110726</v>
       </c>
       <c r="D74" t="n">
-        <v>23.13293328700693</v>
+        <v>23.08151055963358</v>
       </c>
       <c r="E74" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F74" t="n">
-        <v>80.48290065100475</v>
+        <v>83.11864930653832</v>
       </c>
       <c r="G74" t="n">
-        <v>16.18445163881438</v>
+        <v>14.71762884383822</v>
       </c>
       <c r="H74" t="n">
         <v>15</v>
       </c>
       <c r="I74" t="n">
-        <v>587</v>
+        <v>568</v>
       </c>
       <c r="J74" t="n">
-        <v>0.0009910666009621092</v>
+        <v>0.001525883096402865</v>
       </c>
       <c r="K74" t="n">
-        <v>0.02973199802886328</v>
+        <v>0.04577649289208596</v>
       </c>
       <c r="L74" t="b">
         <v>1</v>
@@ -3408,31 +3420,31 @@
         <v>2009</v>
       </c>
       <c r="C75" t="n">
-        <v>78.21960294367388</v>
+        <v>77.79432095057095</v>
       </c>
       <c r="D75" t="n">
-        <v>12.32957510274785</v>
+        <v>11.80483342055276</v>
       </c>
       <c r="E75" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F75" t="n">
-        <v>37.7296118501745</v>
+        <v>38.95815341069908</v>
       </c>
       <c r="G75" t="n">
-        <v>14.20720061567489</v>
+        <v>15.23470207938126</v>
       </c>
       <c r="H75" t="n">
         <v>15</v>
       </c>
       <c r="I75" t="n">
-        <v>734</v>
+        <v>716</v>
       </c>
       <c r="J75" t="n">
-        <v>2.37990784632481e-08</v>
+        <v>3.481759830291977e-08</v>
       </c>
       <c r="K75" t="n">
-        <v>7.13972353897443e-07</v>
+        <v>1.044527949087593e-06</v>
       </c>
       <c r="L75" t="b">
         <v>1</v>
@@ -3448,28 +3460,28 @@
         <v>2010</v>
       </c>
       <c r="C76" t="n">
-        <v>102.0131720350973</v>
+        <v>101.8158530935722</v>
       </c>
       <c r="D76" t="n">
-        <v>16.97287218509999</v>
+        <v>17.2027790918706</v>
       </c>
       <c r="E76" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F76" t="n">
-        <v>112.1742511557692</v>
+        <v>112.4908923483345</v>
       </c>
       <c r="G76" t="n">
-        <v>19.78322204965784</v>
+        <v>19.70847828351005</v>
       </c>
       <c r="H76" t="n">
         <v>15</v>
       </c>
       <c r="I76" t="n">
-        <v>269</v>
+        <v>256</v>
       </c>
       <c r="J76" t="n">
-        <v>0.100458935912733</v>
+        <v>0.07854489397750429</v>
       </c>
       <c r="K76" t="n">
         <v>1</v>
@@ -3488,31 +3500,31 @@
         <v>2011</v>
       </c>
       <c r="C77" t="n">
-        <v>80.46278550806669</v>
+        <v>80.46370581745282</v>
       </c>
       <c r="D77" t="n">
-        <v>15.47078382157</v>
+        <v>15.62515619957442</v>
       </c>
       <c r="E77" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F77" t="n">
-        <v>93.45146183602206</v>
+        <v>88.60855212755905</v>
       </c>
       <c r="G77" t="n">
-        <v>19.54216963317689</v>
+        <v>17.03130428329157</v>
       </c>
       <c r="H77" t="n">
         <v>15</v>
       </c>
       <c r="I77" t="n">
-        <v>232</v>
+        <v>271</v>
       </c>
       <c r="J77" t="n">
-        <v>0.02650564398567578</v>
+        <v>0.1281435904262649</v>
       </c>
       <c r="K77" t="n">
-        <v>0.7951693195702734</v>
+        <v>1</v>
       </c>
       <c r="L77" t="b">
         <v>0</v>
@@ -3528,31 +3540,31 @@
         <v>2012</v>
       </c>
       <c r="C78" t="n">
-        <v>89.52721800169815</v>
+        <v>89.90226448009138</v>
       </c>
       <c r="D78" t="n">
-        <v>12.69486734309036</v>
+        <v>12.40359255034149</v>
       </c>
       <c r="E78" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F78" t="n">
-        <v>73.67083007830921</v>
+        <v>73.92891027455416</v>
       </c>
       <c r="G78" t="n">
-        <v>9.56625254218314</v>
+        <v>9.221370585394952</v>
       </c>
       <c r="H78" t="n">
         <v>15</v>
       </c>
       <c r="I78" t="n">
-        <v>623</v>
+        <v>616</v>
       </c>
       <c r="J78" t="n">
-        <v>0.000116408069911784</v>
+        <v>8.478804582721668e-05</v>
       </c>
       <c r="K78" t="n">
-        <v>0.003492242097353519</v>
+        <v>0.0025436413748165</v>
       </c>
       <c r="L78" t="b">
         <v>1</v>
@@ -3568,31 +3580,31 @@
         <v>2013</v>
       </c>
       <c r="C79" t="n">
-        <v>98.87827376167533</v>
+        <v>98.91188213751369</v>
       </c>
       <c r="D79" t="n">
-        <v>12.59664901111177</v>
+        <v>12.79262848725645</v>
       </c>
       <c r="E79" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F79" t="n">
-        <v>68.37459458439471</v>
+        <v>67.36505519388618</v>
       </c>
       <c r="G79" t="n">
-        <v>5.263671690554039</v>
+        <v>6.133591135065858</v>
       </c>
       <c r="H79" t="n">
         <v>15</v>
       </c>
       <c r="I79" t="n">
-        <v>734</v>
+        <v>720</v>
       </c>
       <c r="J79" t="n">
-        <v>2.37990784632481e-08</v>
+        <v>2.423239797076673e-08</v>
       </c>
       <c r="K79" t="n">
-        <v>7.13972353897443e-07</v>
+        <v>7.269719391230017e-07</v>
       </c>
       <c r="L79" t="b">
         <v>1</v>
@@ -3608,31 +3620,31 @@
         <v>2014</v>
       </c>
       <c r="C80" t="n">
-        <v>93.53478641381244</v>
+        <v>92.88406488097627</v>
       </c>
       <c r="D80" t="n">
-        <v>13.09707111272915</v>
+        <v>12.51459289887789</v>
       </c>
       <c r="E80" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F80" t="n">
-        <v>104.6834542881402</v>
+        <v>104.9921385036322</v>
       </c>
       <c r="G80" t="n">
-        <v>10.97181626200748</v>
+        <v>10.49065576848865</v>
       </c>
       <c r="H80" t="n">
         <v>15</v>
       </c>
       <c r="I80" t="n">
-        <v>197</v>
+        <v>178</v>
       </c>
       <c r="J80" t="n">
-        <v>0.005715509149697121</v>
+        <v>0.002741021773386329</v>
       </c>
       <c r="K80" t="n">
-        <v>0.1714652744909136</v>
+        <v>0.08223065320158986</v>
       </c>
       <c r="L80" t="b">
         <v>0</v>
@@ -3648,31 +3660,31 @@
         <v>2015</v>
       </c>
       <c r="C81" t="n">
-        <v>91.80241868100742</v>
+        <v>92.48162271758382</v>
       </c>
       <c r="D81" t="n">
-        <v>20.7980969636966</v>
+        <v>21.05998516742772</v>
       </c>
       <c r="E81" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F81" t="n">
-        <v>64.16997679026319</v>
+        <v>62.88146051514289</v>
       </c>
       <c r="G81" t="n">
-        <v>8.21906026702357</v>
+        <v>9.152880293634693</v>
       </c>
       <c r="H81" t="n">
         <v>15</v>
       </c>
       <c r="I81" t="n">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="J81" t="n">
-        <v>1.089920689354568e-05</v>
+        <v>5.009483315569529e-06</v>
       </c>
       <c r="K81" t="n">
-        <v>0.0003269762068063703</v>
+        <v>0.0001502844994670859</v>
       </c>
       <c r="L81" t="b">
         <v>1</v>
@@ -3688,31 +3700,31 @@
         <v>2016</v>
       </c>
       <c r="C82" t="n">
-        <v>94.77360962354913</v>
+        <v>95.63249929238579</v>
       </c>
       <c r="D82" t="n">
-        <v>19.29733721143989</v>
+        <v>19.47025703768822</v>
       </c>
       <c r="E82" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F82" t="n">
-        <v>73.27695480705715</v>
+        <v>72.29306840267941</v>
       </c>
       <c r="G82" t="n">
-        <v>16.09622845174097</v>
+        <v>14.70387621564835</v>
       </c>
       <c r="H82" t="n">
         <v>15</v>
       </c>
       <c r="I82" t="n">
-        <v>597</v>
+        <v>605</v>
       </c>
       <c r="J82" t="n">
-        <v>0.0005631871883653079</v>
+        <v>0.0001725729640979386</v>
       </c>
       <c r="K82" t="n">
-        <v>0.01689561565095924</v>
+        <v>0.005177188922938157</v>
       </c>
       <c r="L82" t="b">
         <v>1</v>
@@ -3728,31 +3740,31 @@
         <v>2017</v>
       </c>
       <c r="C83" t="n">
-        <v>95.82151485989223</v>
+        <v>96.23327229561491</v>
       </c>
       <c r="D83" t="n">
-        <v>11.97359921647621</v>
+        <v>11.50660488228949</v>
       </c>
       <c r="E83" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F83" t="n">
-        <v>73.1955969431078</v>
+        <v>76.6492095480705</v>
       </c>
       <c r="G83" t="n">
-        <v>11.37685142019135</v>
+        <v>14.85707759782558</v>
       </c>
       <c r="H83" t="n">
         <v>15</v>
       </c>
       <c r="I83" t="n">
-        <v>676</v>
+        <v>624</v>
       </c>
       <c r="J83" t="n">
-        <v>2.885887738500585e-06</v>
+        <v>4.965695748737155e-05</v>
       </c>
       <c r="K83" t="n">
-        <v>8.657663215501755e-05</v>
+        <v>0.001489708724621146</v>
       </c>
       <c r="L83" t="b">
         <v>1</v>
@@ -3768,28 +3780,28 @@
         <v>2018</v>
       </c>
       <c r="C84" t="n">
-        <v>81.03997939428235</v>
+        <v>81.32429709387281</v>
       </c>
       <c r="D84" t="n">
-        <v>17.77611294158003</v>
+        <v>17.92608217261883</v>
       </c>
       <c r="E84" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F84" t="n">
-        <v>57.99277177092169</v>
+        <v>61.9232353995659</v>
       </c>
       <c r="G84" t="n">
-        <v>39.64115169195732</v>
+        <v>36.88224044180817</v>
       </c>
       <c r="H84" t="n">
         <v>15</v>
       </c>
       <c r="I84" t="n">
-        <v>497</v>
+        <v>479</v>
       </c>
       <c r="J84" t="n">
-        <v>0.05852397352062517</v>
+        <v>0.07854489397750429</v>
       </c>
       <c r="K84" t="n">
         <v>1</v>
@@ -3808,31 +3820,31 @@
         <v>2019</v>
       </c>
       <c r="C85" t="n">
-        <v>83.79591202943656</v>
+        <v>82.99385744900832</v>
       </c>
       <c r="D85" t="n">
-        <v>22.23453777905708</v>
+        <v>21.98841382707166</v>
       </c>
       <c r="E85" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F85" t="n">
-        <v>66.30647721483153</v>
+        <v>68.36174884423052</v>
       </c>
       <c r="G85" t="n">
-        <v>12.63970875287052</v>
+        <v>15.32774235572907</v>
       </c>
       <c r="H85" t="n">
         <v>15</v>
       </c>
       <c r="I85" t="n">
-        <v>551</v>
+        <v>513</v>
       </c>
       <c r="J85" t="n">
-        <v>0.00628497005627164</v>
+        <v>0.02155930376220828</v>
       </c>
       <c r="K85" t="n">
-        <v>0.1885491016881492</v>
+        <v>0.6467791128662485</v>
       </c>
       <c r="L85" t="b">
         <v>0</v>
@@ -3848,28 +3860,28 @@
         <v>2020</v>
       </c>
       <c r="C86" t="n">
-        <v>64.5416361166147</v>
+        <v>64.45307104443808</v>
       </c>
       <c r="D86" t="n">
-        <v>19.18027685787311</v>
+        <v>19.29790822066915</v>
       </c>
       <c r="E86" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F86" t="n">
-        <v>68.65897084630608</v>
+        <v>72.65658684781565</v>
       </c>
       <c r="G86" t="n">
-        <v>42.28961947337806</v>
+        <v>41.30402855150786</v>
       </c>
       <c r="H86" t="n">
         <v>15</v>
       </c>
       <c r="I86" t="n">
-        <v>381</v>
+        <v>328</v>
       </c>
       <c r="J86" t="n">
-        <v>0.9317566669966539</v>
+        <v>0.5365130447184707</v>
       </c>
       <c r="K86" t="n">
         <v>1</v>
@@ -3888,31 +3900,31 @@
         <v>2021</v>
       </c>
       <c r="C87" t="n">
-        <v>103.6495642230396</v>
+        <v>103.2278819526676</v>
       </c>
       <c r="D87" t="n">
-        <v>14.22922016575777</v>
+        <v>14.51103266740867</v>
       </c>
       <c r="E87" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F87" t="n">
-        <v>83.90078007359179</v>
+        <v>82.53041192565334</v>
       </c>
       <c r="G87" t="n">
-        <v>5.579728755444464</v>
+        <v>5.711437278730694</v>
       </c>
       <c r="H87" t="n">
         <v>15</v>
       </c>
       <c r="I87" t="n">
-        <v>652</v>
+        <v>643</v>
       </c>
       <c r="J87" t="n">
-        <v>1.669109541268152e-05</v>
+        <v>1.310414933474819e-05</v>
       </c>
       <c r="K87" t="n">
-        <v>0.0005007328623804455</v>
+        <v>0.0003931244800424457</v>
       </c>
       <c r="L87" t="b">
         <v>1</v>
@@ -3928,31 +3940,31 @@
         <v>2022</v>
       </c>
       <c r="C88" t="n">
-        <v>82.03948519671648</v>
+        <v>82.10052773557749</v>
       </c>
       <c r="D88" t="n">
-        <v>23.34523641553675</v>
+        <v>23.67574005987966</v>
       </c>
       <c r="E88" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F88" t="n">
-        <v>115.4313689970748</v>
+        <v>114.4351421832244</v>
       </c>
       <c r="G88" t="n">
-        <v>9.301549443284166</v>
+        <v>8.366678846801143</v>
       </c>
       <c r="H88" t="n">
         <v>15</v>
       </c>
       <c r="I88" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="J88" t="n">
-        <v>1.443457553510141e-06</v>
+        <v>2.150676326598389e-06</v>
       </c>
       <c r="K88" t="n">
-        <v>4.330372660530422e-05</v>
+        <v>6.452028979795167e-05</v>
       </c>
       <c r="L88" t="b">
         <v>1</v>
@@ -3968,31 +3980,31 @@
         <v>2023</v>
       </c>
       <c r="C89" t="n">
-        <v>99.48820266062812</v>
+        <v>100.4160749088764</v>
       </c>
       <c r="D89" t="n">
-        <v>19.43996936327554</v>
+        <v>19.24635345667291</v>
       </c>
       <c r="E89" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F89" t="n">
-        <v>20.83101726577974</v>
+        <v>21.90550391546367</v>
       </c>
       <c r="G89" t="n">
-        <v>6.063437192625457</v>
+        <v>8.822176441781853</v>
       </c>
       <c r="H89" t="n">
         <v>15</v>
       </c>
       <c r="I89" t="n">
-        <v>750</v>
+        <v>735</v>
       </c>
       <c r="J89" t="n">
-        <v>5.511035590176166e-09</v>
+        <v>6.011850146538538e-09</v>
       </c>
       <c r="K89" t="n">
-        <v>1.65331067705285e-07</v>
+        <v>1.803555043961561e-07</v>
       </c>
       <c r="L89" t="b">
         <v>1</v>
@@ -4008,31 +4020,31 @@
         <v>2024</v>
       </c>
       <c r="C90" t="n">
-        <v>79.27931321822801</v>
+        <v>79.68519740984409</v>
       </c>
       <c r="D90" t="n">
-        <v>17.14445145239728</v>
+        <v>16.93289349065172</v>
       </c>
       <c r="E90" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F90" t="n">
-        <v>104.9698662137933</v>
+        <v>105.6944145674116</v>
       </c>
       <c r="G90" t="n">
-        <v>11.00019646834704</v>
+        <v>11.71774517751746</v>
       </c>
       <c r="H90" t="n">
         <v>15</v>
       </c>
       <c r="I90" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="J90" t="n">
-        <v>7.592324277949792e-06</v>
+        <v>7.286358033927847e-06</v>
       </c>
       <c r="K90" t="n">
-        <v>0.0002277697283384937</v>
+        <v>0.0002185907410178354</v>
       </c>
       <c r="L90" t="b">
         <v>1</v>
@@ -4048,28 +4060,28 @@
         <v>2025</v>
       </c>
       <c r="C91" t="n">
-        <v>80.40680305689206</v>
+        <v>80.48112236233287</v>
       </c>
       <c r="D91" t="n">
-        <v>17.48414000887628</v>
+        <v>17.8347322195845</v>
       </c>
       <c r="E91" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F91" t="n">
-        <v>88.8198445136331</v>
+        <v>90.74601603924872</v>
       </c>
       <c r="G91" t="n">
-        <v>25.66249990749353</v>
+        <v>24.10663885395608</v>
       </c>
       <c r="H91" t="n">
         <v>15</v>
       </c>
       <c r="I91" t="n">
-        <v>277</v>
+        <v>251</v>
       </c>
       <c r="J91" t="n">
-        <v>0.1289960116674873</v>
+        <v>0.06599834109292449</v>
       </c>
       <c r="K91" t="n">
         <v>1</v>
@@ -4088,28 +4100,28 @@
         <v>1996</v>
       </c>
       <c r="C92" t="n">
-        <v>10.04445102505691</v>
+        <v>9.976884030540267</v>
       </c>
       <c r="D92" t="n">
-        <v>4.774877516742245</v>
+        <v>4.77775911400883</v>
       </c>
       <c r="E92" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F92" t="n">
-        <v>10.65142423256315</v>
+        <v>10.66089633727443</v>
       </c>
       <c r="G92" t="n">
-        <v>1.375776704971312</v>
+        <v>1.369864501027699</v>
       </c>
       <c r="H92" t="n">
         <v>15</v>
       </c>
       <c r="I92" t="n">
-        <v>383</v>
+        <v>367</v>
       </c>
       <c r="J92" t="n">
-        <v>0.9070384808036948</v>
+        <v>1</v>
       </c>
       <c r="K92" t="n">
         <v>1</v>
@@ -4128,31 +4140,31 @@
         <v>1997</v>
       </c>
       <c r="C93" t="n">
-        <v>10.61487937954223</v>
+        <v>10.49016018382619</v>
       </c>
       <c r="D93" t="n">
-        <v>5.492183692917293</v>
+        <v>5.239917714851038</v>
       </c>
       <c r="E93" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F93" t="n">
-        <v>14.01680225620995</v>
+        <v>13.53679936363303</v>
       </c>
       <c r="G93" t="n">
-        <v>1.047706997022014</v>
+        <v>1.241571122548622</v>
       </c>
       <c r="H93" t="n">
         <v>15</v>
       </c>
       <c r="I93" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="J93" t="n">
-        <v>0.004948285499472246</v>
+        <v>0.006726157194825958</v>
       </c>
       <c r="K93" t="n">
-        <v>0.1484485649841674</v>
+        <v>0.2017847158447788</v>
       </c>
       <c r="L93" t="b">
         <v>0</v>
@@ -4168,28 +4180,28 @@
         <v>1998</v>
       </c>
       <c r="C94" t="n">
-        <v>13.01218418483563</v>
+        <v>13.00578198086911</v>
       </c>
       <c r="D94" t="n">
-        <v>4.255741956110215</v>
+        <v>4.260755307613882</v>
       </c>
       <c r="E94" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F94" t="n">
-        <v>13.21177170336619</v>
+        <v>12.8638565281845</v>
       </c>
       <c r="G94" t="n">
-        <v>1.924267372385155</v>
+        <v>2.525713671615458</v>
       </c>
       <c r="H94" t="n">
         <v>15</v>
       </c>
       <c r="I94" t="n">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="J94" t="n">
-        <v>0.7144437977797899</v>
+        <v>0.9242421795157034</v>
       </c>
       <c r="K94" t="n">
         <v>1</v>
@@ -4208,31 +4220,31 @@
         <v>1999</v>
       </c>
       <c r="C95" t="n">
-        <v>11.89705640524999</v>
+        <v>11.83047875837607</v>
       </c>
       <c r="D95" t="n">
-        <v>3.212284739641775</v>
+        <v>3.10413081171097</v>
       </c>
       <c r="E95" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F95" t="n">
-        <v>16.40002241747112</v>
+        <v>15.96980438948544</v>
       </c>
       <c r="G95" t="n">
-        <v>1.985638507369884</v>
+        <v>2.099527813156022</v>
       </c>
       <c r="H95" t="n">
         <v>15</v>
       </c>
       <c r="I95" t="n">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="J95" t="n">
-        <v>6.559318429991417e-06</v>
+        <v>2.489808847381998e-05</v>
       </c>
       <c r="K95" t="n">
-        <v>0.0001967795528997425</v>
+        <v>0.0007469426542145995</v>
       </c>
       <c r="L95" t="b">
         <v>1</v>
@@ -4248,28 +4260,28 @@
         <v>2000</v>
       </c>
       <c r="C96" t="n">
-        <v>14.79120121488227</v>
+        <v>14.79094184370783</v>
       </c>
       <c r="D96" t="n">
-        <v>5.483354190788589</v>
+        <v>5.487367802664057</v>
       </c>
       <c r="E96" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F96" t="n">
-        <v>13.94558520446899</v>
+        <v>13.97349604078529</v>
       </c>
       <c r="G96" t="n">
-        <v>1.889401840312159</v>
+        <v>1.887228921330704</v>
       </c>
       <c r="H96" t="n">
         <v>15</v>
       </c>
       <c r="I96" t="n">
-        <v>450</v>
+        <v>436</v>
       </c>
       <c r="J96" t="n">
-        <v>0.2460636969324763</v>
+        <v>0.2811662128313074</v>
       </c>
       <c r="K96" t="n">
         <v>1</v>
@@ -4288,28 +4300,28 @@
         <v>2001</v>
       </c>
       <c r="C97" t="n">
-        <v>11.19955407310985</v>
+        <v>11.17697014373596</v>
       </c>
       <c r="D97" t="n">
-        <v>4.949831466858532</v>
+        <v>4.860922283845525</v>
       </c>
       <c r="E97" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F97" t="n">
-        <v>12.49820479444622</v>
+        <v>12.89502332140142</v>
       </c>
       <c r="G97" t="n">
-        <v>1.416815052253471</v>
+        <v>1.611390280881713</v>
       </c>
       <c r="H97" t="n">
         <v>15</v>
       </c>
       <c r="I97" t="n">
-        <v>292</v>
+        <v>263</v>
       </c>
       <c r="J97" t="n">
-        <v>0.1989589310924021</v>
+        <v>0.09930096774636674</v>
       </c>
       <c r="K97" t="n">
         <v>1</v>
@@ -4328,28 +4340,28 @@
         <v>2002</v>
       </c>
       <c r="C98" t="n">
-        <v>12.26004892070721</v>
+        <v>12.09174320558028</v>
       </c>
       <c r="D98" t="n">
-        <v>4.191941912038186</v>
+        <v>4.029831961507814</v>
       </c>
       <c r="E98" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F98" t="n">
-        <v>11.65834327656647</v>
+        <v>11.60894131684561</v>
       </c>
       <c r="G98" t="n">
-        <v>2.02397563856733</v>
+        <v>1.971670665828901</v>
       </c>
       <c r="H98" t="n">
         <v>15</v>
       </c>
       <c r="I98" t="n">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="J98" t="n">
-        <v>0.9565408509773254</v>
+        <v>0.9620782833741496</v>
       </c>
       <c r="K98" t="n">
         <v>1</v>
@@ -4368,28 +4380,28 @@
         <v>2003</v>
       </c>
       <c r="C99" t="n">
-        <v>12.0744121922117</v>
+        <v>11.98864357327698</v>
       </c>
       <c r="D99" t="n">
-        <v>4.919167532504969</v>
+        <v>4.979278250759188</v>
       </c>
       <c r="E99" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F99" t="n">
-        <v>15.19606284123363</v>
+        <v>14.85432512564625</v>
       </c>
       <c r="G99" t="n">
-        <v>2.51778650056071</v>
+        <v>2.532149039877424</v>
       </c>
       <c r="H99" t="n">
         <v>15</v>
       </c>
       <c r="I99" t="n">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="J99" t="n">
-        <v>0.06063023035647828</v>
+        <v>0.1129986683496688</v>
       </c>
       <c r="K99" t="n">
         <v>1</v>
@@ -4408,28 +4420,28 @@
         <v>2004</v>
       </c>
       <c r="C100" t="n">
-        <v>12.12916205662216</v>
+        <v>12.07781566905965</v>
       </c>
       <c r="D100" t="n">
-        <v>3.09910843295229</v>
+        <v>3.043507738718132</v>
       </c>
       <c r="E100" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F100" t="n">
-        <v>12.43961347940843</v>
+        <v>12.28427595183855</v>
       </c>
       <c r="G100" t="n">
-        <v>1.841415413587176</v>
+        <v>1.694131587790208</v>
       </c>
       <c r="H100" t="n">
         <v>15</v>
       </c>
       <c r="I100" t="n">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="J100" t="n">
-        <v>0.9813671252686654</v>
+        <v>0.9494525195827553</v>
       </c>
       <c r="K100" t="n">
         <v>1</v>
@@ -4448,31 +4460,31 @@
         <v>2005</v>
       </c>
       <c r="C101" t="n">
-        <v>11.96618765592793</v>
+        <v>11.9470807848033</v>
       </c>
       <c r="D101" t="n">
-        <v>2.945137271972132</v>
+        <v>2.929206063601937</v>
       </c>
       <c r="E101" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F101" t="n">
-        <v>13.54913005748993</v>
+        <v>13.49846838051846</v>
       </c>
       <c r="G101" t="n">
-        <v>1.93111254634466</v>
+        <v>1.969920412068354</v>
       </c>
       <c r="H101" t="n">
         <v>15</v>
       </c>
       <c r="I101" t="n">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="J101" t="n">
-        <v>0.02076986676818242</v>
+        <v>0.02247782467889208</v>
       </c>
       <c r="K101" t="n">
-        <v>0.6230960030454726</v>
+        <v>0.6743347403667624</v>
       </c>
       <c r="L101" t="b">
         <v>0</v>
@@ -4488,31 +4500,31 @@
         <v>2006</v>
       </c>
       <c r="C102" t="n">
-        <v>12.21611183425531</v>
+        <v>12.22260095056567</v>
       </c>
       <c r="D102" t="n">
-        <v>4.294374843866394</v>
+        <v>4.267375470214302</v>
       </c>
       <c r="E102" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F102" t="n">
-        <v>17.39511696857933</v>
+        <v>17.01295765990522</v>
       </c>
       <c r="G102" t="n">
-        <v>0.9136891083653985</v>
+        <v>1.06478292257204</v>
       </c>
       <c r="H102" t="n">
         <v>15</v>
       </c>
       <c r="I102" t="n">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="J102" t="n">
-        <v>1.140994790775145e-06</v>
+        <v>6.763581772952894e-06</v>
       </c>
       <c r="K102" t="n">
-        <v>3.422984372325436e-05</v>
+        <v>0.0002029074531885868</v>
       </c>
       <c r="L102" t="b">
         <v>1</v>
@@ -4528,28 +4540,28 @@
         <v>2007</v>
       </c>
       <c r="C103" t="n">
-        <v>13.86416400911158</v>
+        <v>13.7981106012206</v>
       </c>
       <c r="D103" t="n">
-        <v>2.995560214165066</v>
+        <v>2.905133872299771</v>
       </c>
       <c r="E103" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F103" t="n">
-        <v>13.08381169324217</v>
+        <v>13.11198033047686</v>
       </c>
       <c r="G103" t="n">
-        <v>1.599523772470284</v>
+        <v>1.608339748558658</v>
       </c>
       <c r="H103" t="n">
         <v>15</v>
       </c>
       <c r="I103" t="n">
-        <v>442</v>
+        <v>427</v>
       </c>
       <c r="J103" t="n">
-        <v>0.300480467177044</v>
+        <v>0.3497542639778012</v>
       </c>
       <c r="K103" t="n">
         <v>1</v>
@@ -4568,28 +4580,28 @@
         <v>2008</v>
       </c>
       <c r="C104" t="n">
-        <v>12.09923169541162</v>
+        <v>12.11882857275676</v>
       </c>
       <c r="D104" t="n">
-        <v>4.581184878948623</v>
+        <v>4.551538767336544</v>
       </c>
       <c r="E104" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F104" t="n">
-        <v>11.05500415807929</v>
+        <v>10.89258994106371</v>
       </c>
       <c r="G104" t="n">
-        <v>0.520519142915245</v>
+        <v>0.8626102016429978</v>
       </c>
       <c r="H104" t="n">
         <v>15</v>
       </c>
       <c r="I104" t="n">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="J104" t="n">
-        <v>0.7260951618325295</v>
+        <v>0.6457970888947685</v>
       </c>
       <c r="K104" t="n">
         <v>1</v>
@@ -4608,28 +4620,28 @@
         <v>2009</v>
       </c>
       <c r="C105" t="n">
-        <v>14.33787514914845</v>
+        <v>14.27964795420279</v>
       </c>
       <c r="D105" t="n">
-        <v>2.706781094451991</v>
+        <v>2.460025156448743</v>
       </c>
       <c r="E105" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F105" t="n">
-        <v>15.58854611852331</v>
+        <v>15.18299381711679</v>
       </c>
       <c r="G105" t="n">
-        <v>2.234226650808468</v>
+        <v>2.52087068252381</v>
       </c>
       <c r="H105" t="n">
         <v>15</v>
       </c>
       <c r="I105" t="n">
-        <v>258</v>
+        <v>281</v>
       </c>
       <c r="J105" t="n">
-        <v>0.06969273164565185</v>
+        <v>0.1728895624138705</v>
       </c>
       <c r="K105" t="n">
         <v>1</v>
@@ -4648,28 +4660,28 @@
         <v>2010</v>
       </c>
       <c r="C106" t="n">
-        <v>10.91205152402644</v>
+        <v>10.78109870697381</v>
       </c>
       <c r="D106" t="n">
-        <v>2.579162852065092</v>
+        <v>2.663195747484464</v>
       </c>
       <c r="E106" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F106" t="n">
-        <v>12.22784683805182</v>
+        <v>12.24943197020642</v>
       </c>
       <c r="G106" t="n">
-        <v>2.572645104592337</v>
+        <v>2.568280897500115</v>
       </c>
       <c r="H106" t="n">
         <v>15</v>
       </c>
       <c r="I106" t="n">
-        <v>273</v>
+        <v>251</v>
       </c>
       <c r="J106" t="n">
-        <v>0.1140260814386781</v>
+        <v>0.06599834109292449</v>
       </c>
       <c r="K106" t="n">
         <v>1</v>
@@ -4688,31 +4700,31 @@
         <v>2011</v>
       </c>
       <c r="C107" t="n">
-        <v>13.65394576418262</v>
+        <v>13.60260287649062</v>
       </c>
       <c r="D107" t="n">
-        <v>3.281784948869797</v>
+        <v>3.196521977595608</v>
       </c>
       <c r="E107" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F107" t="n">
-        <v>15.98871786527818</v>
+        <v>16.11061358788005</v>
       </c>
       <c r="G107" t="n">
-        <v>1.357925195035609</v>
+        <v>1.403035677809247</v>
       </c>
       <c r="H107" t="n">
         <v>15</v>
       </c>
       <c r="I107" t="n">
-        <v>195</v>
+        <v>169</v>
       </c>
       <c r="J107" t="n">
-        <v>0.005193003141555862</v>
+        <v>0.001700942843893972</v>
       </c>
       <c r="K107" t="n">
-        <v>0.1557900942466759</v>
+        <v>0.05102828531681917</v>
       </c>
       <c r="L107" t="b">
         <v>0</v>
@@ -4728,28 +4740,28 @@
         <v>2012</v>
       </c>
       <c r="C108" t="n">
-        <v>12.10389847054992</v>
+        <v>12.00423216471746</v>
       </c>
       <c r="D108" t="n">
-        <v>4.878606847838874</v>
+        <v>4.892664406692993</v>
       </c>
       <c r="E108" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F108" t="n">
-        <v>13.6925042484723</v>
+        <v>13.42141447011601</v>
       </c>
       <c r="G108" t="n">
-        <v>1.572021939019403</v>
+        <v>1.209552799431394</v>
       </c>
       <c r="H108" t="n">
         <v>15</v>
       </c>
       <c r="I108" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="J108" t="n">
-        <v>0.07462495915346679</v>
+        <v>0.09296720669982936</v>
       </c>
       <c r="K108" t="n">
         <v>1</v>
@@ -4768,28 +4780,28 @@
         <v>2013</v>
       </c>
       <c r="C109" t="n">
-        <v>11.37632942835445</v>
+        <v>11.32213153403238</v>
       </c>
       <c r="D109" t="n">
-        <v>5.804893888617835</v>
+        <v>5.869523900919473</v>
       </c>
       <c r="E109" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F109" t="n">
-        <v>11.60935893263908</v>
+        <v>11.43681382651767</v>
       </c>
       <c r="G109" t="n">
-        <v>1.559362544303027</v>
+        <v>1.779484821339806</v>
       </c>
       <c r="H109" t="n">
         <v>15</v>
       </c>
       <c r="I109" t="n">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="J109" t="n">
-        <v>0.370640749888919</v>
+        <v>0.3920956026993683</v>
       </c>
       <c r="K109" t="n">
         <v>1</v>
@@ -4808,31 +4820,31 @@
         <v>2014</v>
       </c>
       <c r="C110" t="n">
-        <v>12.82010933940771</v>
+        <v>12.74320159563984</v>
       </c>
       <c r="D110" t="n">
-        <v>2.740882719452549</v>
+        <v>2.609789684944342</v>
       </c>
       <c r="E110" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F110" t="n">
-        <v>15.18712730954183</v>
+        <v>14.97182413132294</v>
       </c>
       <c r="G110" t="n">
-        <v>2.355068503962056</v>
+        <v>2.226309223792172</v>
       </c>
       <c r="H110" t="n">
         <v>15</v>
       </c>
       <c r="I110" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J110" t="n">
-        <v>0.005994149149114781</v>
+        <v>0.007054551414920795</v>
       </c>
       <c r="K110" t="n">
-        <v>0.1798244744734434</v>
+        <v>0.2116365424476238</v>
       </c>
       <c r="L110" t="b">
         <v>0</v>
@@ -4848,19 +4860,19 @@
         <v>2015</v>
       </c>
       <c r="C111" t="n">
-        <v>12.22308395704519</v>
+        <v>12.13768780535314</v>
       </c>
       <c r="D111" t="n">
-        <v>4.071693399454347</v>
+        <v>4.1780002474797</v>
       </c>
       <c r="E111" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F111" t="n">
-        <v>13.25344867483816</v>
+        <v>13.04189969989511</v>
       </c>
       <c r="G111" t="n">
-        <v>1.573789251349569</v>
+        <v>1.357378723124335</v>
       </c>
       <c r="H111" t="n">
         <v>15</v>
@@ -4869,7 +4881,7 @@
         <v>354</v>
       </c>
       <c r="J111" t="n">
-        <v>0.7495865590587008</v>
+        <v>0.8367663045467267</v>
       </c>
       <c r="K111" t="n">
         <v>1</v>
@@ -4888,31 +4900,31 @@
         <v>2016</v>
       </c>
       <c r="C112" t="n">
-        <v>11.95184260765807</v>
+        <v>11.8876599126471</v>
       </c>
       <c r="D112" t="n">
-        <v>3.411764535707374</v>
+        <v>3.393835426481342</v>
       </c>
       <c r="E112" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F112" t="n">
-        <v>15.99555627869975</v>
+        <v>15.77569295295942</v>
       </c>
       <c r="G112" t="n">
-        <v>0.8510238288676563</v>
+        <v>1.17719001678617</v>
       </c>
       <c r="H112" t="n">
         <v>15</v>
       </c>
       <c r="I112" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="J112" t="n">
-        <v>0.0001498669228237431</v>
+        <v>0.0002084354895696077</v>
       </c>
       <c r="K112" t="n">
-        <v>0.004496007684712293</v>
+        <v>0.006253064687088229</v>
       </c>
       <c r="L112" t="b">
         <v>1</v>
@@ -4928,31 +4940,31 @@
         <v>2017</v>
       </c>
       <c r="C113" t="n">
-        <v>11.40620208265535</v>
+        <v>11.34521529405771</v>
       </c>
       <c r="D113" t="n">
-        <v>3.905868930242533</v>
+        <v>3.902337112785027</v>
       </c>
       <c r="E113" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F113" t="n">
-        <v>13.9487044871099</v>
+        <v>13.93300900314563</v>
       </c>
       <c r="G113" t="n">
-        <v>1.074690847646337</v>
+        <v>1.092047022789016</v>
       </c>
       <c r="H113" t="n">
         <v>15</v>
       </c>
       <c r="I113" t="n">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="J113" t="n">
-        <v>0.002588571976172922</v>
+        <v>0.002886886199696116</v>
       </c>
       <c r="K113" t="n">
-        <v>0.07765715928518765</v>
+        <v>0.08660658599088349</v>
       </c>
       <c r="L113" t="b">
         <v>0</v>
@@ -4968,28 +4980,28 @@
         <v>2018</v>
       </c>
       <c r="C114" t="n">
-        <v>15.62549040026028</v>
+        <v>15.5345672535203</v>
       </c>
       <c r="D114" t="n">
-        <v>3.669972852095712</v>
+        <v>3.893259985312178</v>
       </c>
       <c r="E114" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F114" t="n">
-        <v>14.09701305275332</v>
+        <v>13.40797953501821</v>
       </c>
       <c r="G114" t="n">
-        <v>4.219541922005324</v>
+        <v>3.951027162006844</v>
       </c>
       <c r="H114" t="n">
         <v>15</v>
       </c>
       <c r="I114" t="n">
-        <v>467</v>
+        <v>499</v>
       </c>
       <c r="J114" t="n">
-        <v>0.1542575118326619</v>
+        <v>0.03787882334931163</v>
       </c>
       <c r="K114" t="n">
         <v>1</v>
@@ -5008,34 +5020,34 @@
         <v>2019</v>
       </c>
       <c r="C115" t="n">
-        <v>12.00679021585851</v>
+        <v>11.89462379159274</v>
       </c>
       <c r="D115" t="n">
-        <v>2.803967014712943</v>
+        <v>2.849357269857747</v>
       </c>
       <c r="E115" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F115" t="n">
-        <v>14.34362078316515</v>
+        <v>14.14557110315647</v>
       </c>
       <c r="G115" t="n">
-        <v>1.401667123261786</v>
+        <v>1.815622690808194</v>
       </c>
       <c r="H115" t="n">
         <v>15</v>
       </c>
       <c r="I115" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="J115" t="n">
-        <v>0.001303533771068182</v>
+        <v>0.001795234396139357</v>
       </c>
       <c r="K115" t="n">
-        <v>0.03910601313204547</v>
+        <v>0.05385703188418071</v>
       </c>
       <c r="L115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -5048,31 +5060,31 @@
         <v>2020</v>
       </c>
       <c r="C116" t="n">
-        <v>12.71817854431062</v>
+        <v>12.64679499525156</v>
       </c>
       <c r="D116" t="n">
-        <v>3.214255433447994</v>
+        <v>3.161639695897647</v>
       </c>
       <c r="E116" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F116" t="n">
-        <v>15.02372817008348</v>
+        <v>14.95757963625841</v>
       </c>
       <c r="G116" t="n">
-        <v>2.748340662371178</v>
+        <v>2.713265275172892</v>
       </c>
       <c r="H116" t="n">
         <v>15</v>
       </c>
       <c r="I116" t="n">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="J116" t="n">
-        <v>0.01911493836954378</v>
+        <v>0.01599701201631716</v>
       </c>
       <c r="K116" t="n">
-        <v>0.5734481510863133</v>
+        <v>0.4799103604895149</v>
       </c>
       <c r="L116" t="b">
         <v>0</v>
@@ -5088,31 +5100,31 @@
         <v>2021</v>
       </c>
       <c r="C117" t="n">
-        <v>10.06537455255448</v>
+        <v>9.984456568178823</v>
       </c>
       <c r="D117" t="n">
-        <v>3.876373618382735</v>
+        <v>3.87275875198019</v>
       </c>
       <c r="E117" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F117" t="n">
-        <v>14.89377625917485</v>
+        <v>14.99216690168851</v>
       </c>
       <c r="G117" t="n">
-        <v>1.764110647249256</v>
+        <v>1.80140081861583</v>
       </c>
       <c r="H117" t="n">
         <v>15</v>
       </c>
       <c r="I117" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="J117" t="n">
-        <v>7.592324277949792e-06</v>
+        <v>5.401896369003672e-06</v>
       </c>
       <c r="K117" t="n">
-        <v>0.0002277697283384937</v>
+        <v>0.0001620568910701102</v>
       </c>
       <c r="L117" t="b">
         <v>1</v>
@@ -5128,28 +5140,28 @@
         <v>2022</v>
       </c>
       <c r="C118" t="n">
-        <v>12.91147214710651</v>
+        <v>12.65543967505874</v>
       </c>
       <c r="D118" t="n">
-        <v>5.305711032379733</v>
+        <v>5.294137600825671</v>
       </c>
       <c r="E118" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F118" t="n">
-        <v>11.81033387416616</v>
+        <v>11.83037714079678</v>
       </c>
       <c r="G118" t="n">
-        <v>1.419815861036465</v>
+        <v>1.409488782793698</v>
       </c>
       <c r="H118" t="n">
         <v>15</v>
       </c>
       <c r="I118" t="n">
-        <v>405</v>
+        <v>390</v>
       </c>
       <c r="J118" t="n">
-        <v>0.6460084249117091</v>
+        <v>0.7273380490354202</v>
       </c>
       <c r="K118" t="n">
         <v>1</v>
@@ -5168,31 +5180,31 @@
         <v>2023</v>
       </c>
       <c r="C119" t="n">
-        <v>11.49655619253648</v>
+        <v>11.39683723137711</v>
       </c>
       <c r="D119" t="n">
-        <v>3.724739644583686</v>
+        <v>3.69016840301863</v>
       </c>
       <c r="E119" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F119" t="n">
-        <v>18.20456499008469</v>
+        <v>18.0085657111952</v>
       </c>
       <c r="G119" t="n">
-        <v>1.702436848019746</v>
+        <v>1.510991406644872</v>
       </c>
       <c r="H119" t="n">
         <v>15</v>
       </c>
       <c r="I119" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J119" t="n">
-        <v>8.146307839310267e-08</v>
+        <v>8.469987578433327e-08</v>
       </c>
       <c r="K119" t="n">
-        <v>2.44389235179308e-06</v>
+        <v>2.540996273529998e-06</v>
       </c>
       <c r="L119" t="b">
         <v>1</v>
@@ -5208,28 +5220,28 @@
         <v>2024</v>
       </c>
       <c r="C120" t="n">
-        <v>14.72036538669547</v>
+        <v>14.62035882606148</v>
       </c>
       <c r="D120" t="n">
-        <v>4.350649794276738</v>
+        <v>4.35365453592888</v>
       </c>
       <c r="E120" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F120" t="n">
-        <v>15.01505173967906</v>
+        <v>14.5883601946998</v>
       </c>
       <c r="G120" t="n">
-        <v>2.559483505388361</v>
+        <v>2.684023191633117</v>
       </c>
       <c r="H120" t="n">
         <v>15</v>
       </c>
       <c r="I120" t="n">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="J120" t="n">
-        <v>0.6798964474237625</v>
+        <v>0.5576085245106175</v>
       </c>
       <c r="K120" t="n">
         <v>1</v>
@@ -5248,28 +5260,28 @@
         <v>2025</v>
       </c>
       <c r="C121" t="n">
-        <v>14.18535316387233</v>
+        <v>14.13087603889578</v>
       </c>
       <c r="D121" t="n">
-        <v>3.433671319075306</v>
+        <v>3.402120520107269</v>
       </c>
       <c r="E121" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F121" t="n">
-        <v>14.01399927888945</v>
+        <v>13.59126374616905</v>
       </c>
       <c r="G121" t="n">
-        <v>3.440979017127117</v>
+        <v>3.4859187281414</v>
       </c>
       <c r="H121" t="n">
         <v>15</v>
       </c>
       <c r="I121" t="n">
-        <v>421</v>
+        <v>440</v>
       </c>
       <c r="J121" t="n">
-        <v>0.4786757603358271</v>
+        <v>0.2538293321771464</v>
       </c>
       <c r="K121" t="n">
         <v>1</v>
